--- a/web/src/main/webapp/StorageYard/Other/UserDoc/Payroll/Staff Info for HRMS Demo.xlsx
+++ b/web/src/main/webapp/StorageYard/Other/UserDoc/Payroll/Staff Info for HRMS Demo.xlsx
@@ -534,13 +534,13 @@
     <t>Retainership</t>
   </si>
   <si>
-    <t>nd7</t>
-  </si>
-  <si>
     <t>Flydocs</t>
   </si>
   <si>
     <t>O -ve</t>
+  </si>
+  <si>
+    <t>00nd7</t>
   </si>
 </sst>
 </file>
@@ -926,9 +926,6 @@
     <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1052,6 +1049,27 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="8" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="7" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1059,10 +1077,34 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="7" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="5" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="7" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1070,21 +1112,6 @@
     <xf numFmtId="14" fontId="7" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -1097,35 +1124,8 @@
     <xf numFmtId="14" fontId="8" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="5" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1455,66 +1455,66 @@
     <col min="2" max="2" width="6" style="4" customWidth="1"/>
     <col min="3" max="3" width="13.7109375" style="3" customWidth="1"/>
     <col min="4" max="4" width="6.28515625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" style="55" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" style="54" customWidth="1"/>
     <col min="6" max="6" width="8.140625" style="3" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" style="56" customWidth="1"/>
-    <col min="9" max="9" width="24.5703125" style="56" customWidth="1"/>
-    <col min="10" max="10" width="39.7109375" style="55" customWidth="1"/>
-    <col min="11" max="11" width="19" style="55" customWidth="1"/>
-    <col min="12" max="12" width="36.140625" style="56" customWidth="1"/>
-    <col min="13" max="14" width="16.140625" style="56" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" style="56" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" style="55" customWidth="1"/>
+    <col min="9" max="9" width="24.5703125" style="55" customWidth="1"/>
+    <col min="10" max="10" width="39.7109375" style="54" customWidth="1"/>
+    <col min="11" max="11" width="19" style="54" customWidth="1"/>
+    <col min="12" max="12" width="36.140625" style="55" customWidth="1"/>
+    <col min="13" max="14" width="16.140625" style="55" customWidth="1"/>
+    <col min="15" max="15" width="13.85546875" style="55" customWidth="1"/>
     <col min="16" max="16" width="28.28515625" style="3" customWidth="1" outlineLevel="1"/>
     <col min="17" max="17" width="17.7109375" style="3" customWidth="1" outlineLevel="1"/>
     <col min="18" max="18" width="27.42578125" style="3" customWidth="1" outlineLevel="1"/>
     <col min="19" max="19" width="14" style="3" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="20" width="12" style="55" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="22" width="16.85546875" style="55" customWidth="1" outlineLevel="1"/>
-    <col min="23" max="26" width="12.140625" style="55" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="12" style="54" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="22" width="16.85546875" style="54" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="26" width="12.140625" style="54" customWidth="1" outlineLevel="1"/>
     <col min="27" max="27" width="6" style="3" customWidth="1"/>
-    <col min="28" max="28" width="98" style="55" customWidth="1" outlineLevel="1"/>
-    <col min="29" max="29" width="26.28515625" style="55" customWidth="1" outlineLevel="1"/>
+    <col min="28" max="28" width="98" style="54" customWidth="1" outlineLevel="1"/>
+    <col min="29" max="29" width="26.28515625" style="54" customWidth="1" outlineLevel="1"/>
     <col min="30" max="30" width="12.28515625" style="3" customWidth="1" outlineLevel="1"/>
     <col min="31" max="31" width="12" style="3" customWidth="1" outlineLevel="1"/>
     <col min="32" max="32" width="10.5703125" style="3" customWidth="1" outlineLevel="1"/>
     <col min="33" max="33" width="8.85546875" style="3" customWidth="1" outlineLevel="1"/>
     <col min="34" max="34" width="6" style="3" customWidth="1"/>
-    <col min="35" max="35" width="51.28515625" style="55" customWidth="1" outlineLevel="1"/>
-    <col min="36" max="36" width="45" style="55" customWidth="1" outlineLevel="1"/>
-    <col min="37" max="37" width="25.140625" style="55" customWidth="1" outlineLevel="1"/>
+    <col min="35" max="35" width="51.28515625" style="54" customWidth="1" outlineLevel="1"/>
+    <col min="36" max="36" width="45" style="54" customWidth="1" outlineLevel="1"/>
+    <col min="37" max="37" width="25.140625" style="54" customWidth="1" outlineLevel="1"/>
     <col min="38" max="38" width="16.42578125" style="3" customWidth="1" outlineLevel="1"/>
     <col min="39" max="39" width="10.5703125" style="3" customWidth="1" outlineLevel="1"/>
     <col min="40" max="40" width="8.85546875" style="3" customWidth="1" outlineLevel="1"/>
     <col min="41" max="41" width="6" style="3" customWidth="1"/>
     <col min="42" max="42" width="41.140625" style="3" customWidth="1" outlineLevel="1"/>
     <col min="43" max="43" width="39.140625" style="3" customWidth="1" outlineLevel="1"/>
-    <col min="44" max="44" width="38.5703125" style="55" customWidth="1" outlineLevel="1"/>
+    <col min="44" max="44" width="38.5703125" style="54" customWidth="1" outlineLevel="1"/>
     <col min="45" max="45" width="63.85546875" style="3" customWidth="1" outlineLevel="1"/>
     <col min="46" max="46" width="6" style="3" customWidth="1"/>
-    <col min="47" max="47" width="21.7109375" style="57" customWidth="1" outlineLevel="1"/>
+    <col min="47" max="47" width="21.7109375" style="56" customWidth="1" outlineLevel="1"/>
     <col min="48" max="49" width="21.7109375" style="5" customWidth="1" outlineLevel="1"/>
     <col min="50" max="50" width="20.42578125" style="3" customWidth="1" outlineLevel="1"/>
     <col min="51" max="51" width="24.5703125" style="3" customWidth="1" outlineLevel="1"/>
-    <col min="52" max="52" width="24.5703125" style="58" customWidth="1" outlineLevel="1"/>
+    <col min="52" max="52" width="24.5703125" style="57" customWidth="1" outlineLevel="1"/>
     <col min="53" max="53" width="15.28515625" style="3" customWidth="1" outlineLevel="1"/>
-    <col min="54" max="54" width="13.5703125" style="58" customWidth="1" outlineLevel="1"/>
-    <col min="55" max="55" width="16.28515625" style="58" customWidth="1" outlineLevel="1"/>
-    <col min="56" max="56" width="11" style="58" customWidth="1" outlineLevel="1"/>
-    <col min="57" max="57" width="13.140625" style="58" customWidth="1" outlineLevel="1"/>
+    <col min="54" max="54" width="13.5703125" style="57" customWidth="1" outlineLevel="1"/>
+    <col min="55" max="55" width="16.28515625" style="57" customWidth="1" outlineLevel="1"/>
+    <col min="56" max="56" width="11" style="57" customWidth="1" outlineLevel="1"/>
+    <col min="57" max="57" width="13.140625" style="57" customWidth="1" outlineLevel="1"/>
     <col min="58" max="58" width="6" style="3" customWidth="1"/>
     <col min="59" max="59" width="15" style="3" customWidth="1" outlineLevel="1"/>
     <col min="60" max="60" width="17.7109375" style="3" customWidth="1" outlineLevel="1"/>
     <col min="61" max="61" width="13.5703125" style="3" customWidth="1" outlineLevel="1"/>
     <col min="62" max="62" width="27" style="3" customWidth="1" outlineLevel="1"/>
     <col min="63" max="63" width="6" style="3" customWidth="1"/>
-    <col min="64" max="64" width="45" style="56" customWidth="1" outlineLevel="1"/>
-    <col min="65" max="65" width="29.85546875" style="56" customWidth="1" outlineLevel="1"/>
+    <col min="64" max="64" width="45" style="55" customWidth="1" outlineLevel="1"/>
+    <col min="65" max="65" width="29.85546875" style="55" customWidth="1" outlineLevel="1"/>
     <col min="66" max="66" width="6" style="3" customWidth="1"/>
-    <col min="67" max="67" width="19" style="56" customWidth="1" outlineLevel="1"/>
-    <col min="68" max="68" width="33" style="56" customWidth="1" outlineLevel="1"/>
-    <col min="69" max="69" width="21.7109375" style="56" customWidth="1" outlineLevel="1"/>
-    <col min="70" max="70" width="18.7109375" style="56" customWidth="1" outlineLevel="1"/>
+    <col min="67" max="67" width="19" style="55" customWidth="1" outlineLevel="1"/>
+    <col min="68" max="68" width="33" style="55" customWidth="1" outlineLevel="1"/>
+    <col min="69" max="69" width="21.7109375" style="55" customWidth="1" outlineLevel="1"/>
+    <col min="70" max="70" width="18.7109375" style="55" customWidth="1" outlineLevel="1"/>
     <col min="71" max="71" width="35.140625" style="3" customWidth="1" outlineLevel="1"/>
     <col min="72" max="72" width="21.7109375" style="3" customWidth="1" outlineLevel="1"/>
     <col min="73" max="73" width="18.7109375" style="3" customWidth="1" outlineLevel="1"/>
@@ -1532,11 +1532,11 @@
     <col min="85" max="85" width="13.5703125" style="3" customWidth="1" outlineLevel="1"/>
     <col min="86" max="86" width="26.85546875" style="3" customWidth="1" outlineLevel="1"/>
     <col min="87" max="87" width="50.7109375" style="3" customWidth="1" outlineLevel="1"/>
-    <col min="88" max="88" width="78.7109375" style="59" customWidth="1" outlineLevel="1"/>
+    <col min="88" max="88" width="78.7109375" style="58" customWidth="1" outlineLevel="1"/>
     <col min="89" max="89" width="6" style="3" customWidth="1"/>
-    <col min="90" max="90" width="21.85546875" style="55" customWidth="1" outlineLevel="1"/>
-    <col min="91" max="91" width="18.5703125" style="55" customWidth="1" outlineLevel="1"/>
-    <col min="92" max="92" width="22" style="56" customWidth="1" outlineLevel="1"/>
+    <col min="90" max="90" width="21.85546875" style="54" customWidth="1" outlineLevel="1"/>
+    <col min="91" max="91" width="18.5703125" style="54" customWidth="1" outlineLevel="1"/>
+    <col min="92" max="92" width="22" style="55" customWidth="1" outlineLevel="1"/>
     <col min="93" max="93" width="6" style="3" customWidth="1"/>
     <col min="94" max="94" width="53.7109375" style="3" customWidth="1"/>
     <col min="95" max="95" width="46.28515625" style="3" customWidth="1"/>
@@ -1583,10 +1583,10 @@
       <c r="U1" s="13"/>
       <c r="V1" s="13"/>
       <c r="W1" s="13"/>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="39"/>
-      <c r="Z1" s="39"/>
-      <c r="AA1" s="72" t="s">
+      <c r="X1" s="38"/>
+      <c r="Y1" s="38"/>
+      <c r="Z1" s="38"/>
+      <c r="AA1" s="62" t="s">
         <v>79</v>
       </c>
       <c r="AB1" s="13"/>
@@ -1595,7 +1595,7 @@
       <c r="AE1" s="13"/>
       <c r="AF1" s="13"/>
       <c r="AG1" s="13"/>
-      <c r="AH1" s="72" t="s">
+      <c r="AH1" s="62" t="s">
         <v>82</v>
       </c>
       <c r="AI1" s="13"/>
@@ -1604,84 +1604,84 @@
       <c r="AL1" s="13"/>
       <c r="AM1" s="13"/>
       <c r="AN1" s="13"/>
-      <c r="AO1" s="72" t="s">
+      <c r="AO1" s="62" t="s">
         <v>83</v>
       </c>
       <c r="AP1" s="13"/>
       <c r="AQ1" s="13"/>
       <c r="AR1" s="13"/>
       <c r="AS1" s="13"/>
-      <c r="AT1" s="72" t="s">
+      <c r="AT1" s="62" t="s">
         <v>84</v>
       </c>
-      <c r="AU1" s="74"/>
-      <c r="AV1" s="75"/>
-      <c r="AW1" s="75"/>
-      <c r="AX1" s="75"/>
-      <c r="AY1" s="75"/>
-      <c r="AZ1" s="76"/>
-      <c r="BA1" s="75"/>
-      <c r="BB1" s="76"/>
-      <c r="BC1" s="76"/>
-      <c r="BD1" s="76"/>
-      <c r="BE1" s="77"/>
-      <c r="BF1" s="72" t="s">
+      <c r="AU1" s="83"/>
+      <c r="AV1" s="84"/>
+      <c r="AW1" s="84"/>
+      <c r="AX1" s="84"/>
+      <c r="AY1" s="84"/>
+      <c r="AZ1" s="85"/>
+      <c r="BA1" s="84"/>
+      <c r="BB1" s="85"/>
+      <c r="BC1" s="85"/>
+      <c r="BD1" s="85"/>
+      <c r="BE1" s="86"/>
+      <c r="BF1" s="62" t="s">
         <v>85</v>
       </c>
       <c r="BG1" s="14"/>
       <c r="BH1" s="15"/>
       <c r="BI1" s="15"/>
       <c r="BJ1" s="16"/>
-      <c r="BK1" s="72" t="s">
+      <c r="BK1" s="62" t="s">
         <v>87</v>
       </c>
-      <c r="BL1" s="86"/>
-      <c r="BM1" s="71"/>
-      <c r="BN1" s="72" t="s">
+      <c r="BL1" s="75"/>
+      <c r="BM1" s="76"/>
+      <c r="BN1" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="BO1" s="69"/>
-      <c r="BP1" s="70"/>
-      <c r="BQ1" s="70"/>
-      <c r="BR1" s="71"/>
-      <c r="BS1" s="69"/>
-      <c r="BT1" s="70"/>
-      <c r="BU1" s="70"/>
-      <c r="BV1" s="71"/>
-      <c r="BW1" s="69"/>
-      <c r="BX1" s="70"/>
-      <c r="BY1" s="70"/>
-      <c r="BZ1" s="71"/>
-      <c r="CA1" s="69"/>
-      <c r="CB1" s="70"/>
-      <c r="CC1" s="70"/>
-      <c r="CD1" s="71"/>
-      <c r="CE1" s="72" t="s">
+      <c r="BO1" s="77"/>
+      <c r="BP1" s="78"/>
+      <c r="BQ1" s="78"/>
+      <c r="BR1" s="76"/>
+      <c r="BS1" s="77"/>
+      <c r="BT1" s="78"/>
+      <c r="BU1" s="78"/>
+      <c r="BV1" s="76"/>
+      <c r="BW1" s="77"/>
+      <c r="BX1" s="78"/>
+      <c r="BY1" s="78"/>
+      <c r="BZ1" s="76"/>
+      <c r="CA1" s="77"/>
+      <c r="CB1" s="78"/>
+      <c r="CC1" s="78"/>
+      <c r="CD1" s="76"/>
+      <c r="CE1" s="62" t="s">
         <v>75</v>
       </c>
       <c r="CF1" s="15"/>
       <c r="CG1" s="15"/>
       <c r="CH1" s="15"/>
       <c r="CI1" s="15"/>
-      <c r="CJ1" s="40"/>
-      <c r="CK1" s="72" t="s">
+      <c r="CJ1" s="39"/>
+      <c r="CK1" s="62" t="s">
         <v>77</v>
       </c>
       <c r="CL1" s="15"/>
       <c r="CM1" s="15"/>
       <c r="CN1" s="15"/>
-      <c r="CO1" s="72" t="s">
+      <c r="CO1" s="62" t="s">
         <v>86</v>
       </c>
       <c r="CP1" s="15"/>
       <c r="CQ1" s="15"/>
       <c r="CR1" s="15"/>
-      <c r="CS1" s="41"/>
-      <c r="CT1" s="41"/>
+      <c r="CS1" s="40"/>
+      <c r="CT1" s="40"/>
       <c r="CU1" s="15"/>
       <c r="CV1" s="15"/>
       <c r="CW1" s="15"/>
-      <c r="CX1" s="78" t="s">
+      <c r="CX1" s="64" t="s">
         <v>101</v>
       </c>
       <c r="CY1" s="15"/>
@@ -1697,139 +1697,139 @@
     <row r="2" spans="1:111" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9"/>
       <c r="B2" s="9"/>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="79"/>
-      <c r="E2" s="37" t="s">
+      <c r="D2" s="65"/>
+      <c r="E2" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="31" t="s">
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="34"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="87"/>
-      <c r="AB2" s="80" t="s">
+      <c r="Q2" s="31"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="33"/>
+      <c r="T2" s="34"/>
+      <c r="U2" s="34"/>
+      <c r="V2" s="34"/>
+      <c r="W2" s="34"/>
+      <c r="X2" s="34"/>
+      <c r="Y2" s="34"/>
+      <c r="Z2" s="34"/>
+      <c r="AA2" s="79"/>
+      <c r="AB2" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="AC2" s="81"/>
-      <c r="AD2" s="81"/>
-      <c r="AE2" s="81"/>
-      <c r="AF2" s="81"/>
-      <c r="AG2" s="82"/>
-      <c r="AH2" s="73"/>
-      <c r="AI2" s="63" t="s">
+      <c r="AC2" s="67"/>
+      <c r="AD2" s="67"/>
+      <c r="AE2" s="67"/>
+      <c r="AF2" s="67"/>
+      <c r="AG2" s="68"/>
+      <c r="AH2" s="63"/>
+      <c r="AI2" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="AJ2" s="64"/>
-      <c r="AK2" s="64"/>
-      <c r="AL2" s="64"/>
-      <c r="AM2" s="64"/>
-      <c r="AN2" s="66"/>
-      <c r="AO2" s="73"/>
-      <c r="AP2" s="34" t="s">
+      <c r="AJ2" s="70"/>
+      <c r="AK2" s="70"/>
+      <c r="AL2" s="70"/>
+      <c r="AM2" s="70"/>
+      <c r="AN2" s="71"/>
+      <c r="AO2" s="63"/>
+      <c r="AP2" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="AQ2" s="35"/>
-      <c r="AR2" s="35"/>
-      <c r="AS2" s="36"/>
-      <c r="AT2" s="73"/>
-      <c r="AU2" s="83" t="s">
+      <c r="AQ2" s="34"/>
+      <c r="AR2" s="34"/>
+      <c r="AS2" s="35"/>
+      <c r="AT2" s="63"/>
+      <c r="AU2" s="72" t="s">
         <v>91</v>
       </c>
-      <c r="AV2" s="64"/>
-      <c r="AW2" s="64"/>
-      <c r="AX2" s="64"/>
-      <c r="AY2" s="64"/>
-      <c r="AZ2" s="84"/>
-      <c r="BA2" s="64"/>
-      <c r="BB2" s="84"/>
-      <c r="BC2" s="84"/>
-      <c r="BD2" s="84"/>
-      <c r="BE2" s="85"/>
-      <c r="BF2" s="73"/>
-      <c r="BG2" s="63" t="s">
+      <c r="AV2" s="70"/>
+      <c r="AW2" s="70"/>
+      <c r="AX2" s="70"/>
+      <c r="AY2" s="70"/>
+      <c r="AZ2" s="73"/>
+      <c r="BA2" s="70"/>
+      <c r="BB2" s="73"/>
+      <c r="BC2" s="73"/>
+      <c r="BD2" s="73"/>
+      <c r="BE2" s="74"/>
+      <c r="BF2" s="63"/>
+      <c r="BG2" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="BH2" s="64"/>
-      <c r="BI2" s="64"/>
-      <c r="BJ2" s="66"/>
-      <c r="BK2" s="73"/>
-      <c r="BL2" s="63" t="s">
+      <c r="BH2" s="70"/>
+      <c r="BI2" s="70"/>
+      <c r="BJ2" s="71"/>
+      <c r="BK2" s="63"/>
+      <c r="BL2" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="BM2" s="66"/>
-      <c r="BN2" s="73"/>
-      <c r="BO2" s="63" t="s">
+      <c r="BM2" s="71"/>
+      <c r="BN2" s="63"/>
+      <c r="BO2" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="BP2" s="64"/>
-      <c r="BQ2" s="64"/>
-      <c r="BR2" s="64"/>
-      <c r="BS2" s="64"/>
-      <c r="BT2" s="64"/>
-      <c r="BU2" s="64"/>
-      <c r="BV2" s="64"/>
-      <c r="BW2" s="64"/>
-      <c r="BX2" s="64"/>
-      <c r="BY2" s="64"/>
-      <c r="BZ2" s="64"/>
-      <c r="CA2" s="64"/>
-      <c r="CB2" s="64"/>
-      <c r="CC2" s="64"/>
-      <c r="CD2" s="66"/>
-      <c r="CE2" s="73"/>
-      <c r="CF2" s="63" t="s">
+      <c r="BP2" s="70"/>
+      <c r="BQ2" s="70"/>
+      <c r="BR2" s="70"/>
+      <c r="BS2" s="70"/>
+      <c r="BT2" s="70"/>
+      <c r="BU2" s="70"/>
+      <c r="BV2" s="70"/>
+      <c r="BW2" s="70"/>
+      <c r="BX2" s="70"/>
+      <c r="BY2" s="70"/>
+      <c r="BZ2" s="70"/>
+      <c r="CA2" s="70"/>
+      <c r="CB2" s="70"/>
+      <c r="CC2" s="70"/>
+      <c r="CD2" s="71"/>
+      <c r="CE2" s="63"/>
+      <c r="CF2" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="CG2" s="64"/>
-      <c r="CH2" s="64"/>
-      <c r="CI2" s="64"/>
-      <c r="CJ2" s="65"/>
-      <c r="CK2" s="73"/>
-      <c r="CL2" s="63" t="s">
+      <c r="CG2" s="70"/>
+      <c r="CH2" s="70"/>
+      <c r="CI2" s="70"/>
+      <c r="CJ2" s="80"/>
+      <c r="CK2" s="63"/>
+      <c r="CL2" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="CM2" s="64"/>
-      <c r="CN2" s="66"/>
-      <c r="CO2" s="73"/>
-      <c r="CP2" s="43"/>
-      <c r="CQ2" s="42"/>
-      <c r="CR2" s="44"/>
-      <c r="CS2" s="45"/>
-      <c r="CT2" s="45"/>
-      <c r="CU2" s="44"/>
-      <c r="CV2" s="44"/>
-      <c r="CW2" s="44"/>
-      <c r="CX2" s="78"/>
-      <c r="CY2" s="44"/>
-      <c r="CZ2" s="44"/>
-      <c r="DA2" s="44"/>
-      <c r="DB2" s="44"/>
-      <c r="DC2" s="44"/>
-      <c r="DD2" s="44"/>
-      <c r="DE2" s="44"/>
-      <c r="DF2" s="44"/>
-      <c r="DG2" s="44"/>
+      <c r="CM2" s="70"/>
+      <c r="CN2" s="71"/>
+      <c r="CO2" s="63"/>
+      <c r="CP2" s="42"/>
+      <c r="CQ2" s="41"/>
+      <c r="CR2" s="43"/>
+      <c r="CS2" s="44"/>
+      <c r="CT2" s="44"/>
+      <c r="CU2" s="43"/>
+      <c r="CV2" s="43"/>
+      <c r="CW2" s="43"/>
+      <c r="CX2" s="64"/>
+      <c r="CY2" s="43"/>
+      <c r="CZ2" s="43"/>
+      <c r="DA2" s="43"/>
+      <c r="DB2" s="43"/>
+      <c r="DC2" s="43"/>
+      <c r="DD2" s="43"/>
+      <c r="DE2" s="43"/>
+      <c r="DF2" s="43"/>
+      <c r="DG2" s="43"/>
     </row>
     <row r="3" spans="1:111" s="8" customFormat="1" ht="115.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
@@ -1868,13 +1868,13 @@
       <c r="L3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="46" t="s">
+      <c r="M3" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="N3" s="46" t="s">
+      <c r="N3" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="O3" s="46" t="s">
+      <c r="O3" s="45" t="s">
         <v>105</v>
       </c>
       <c r="P3" s="7" t="s">
@@ -1895,26 +1895,26 @@
       <c r="U3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="V3" s="46" t="s">
+      <c r="V3" s="45" t="s">
         <v>106</v>
       </c>
       <c r="W3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="X3" s="46" t="s">
+      <c r="X3" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="Y3" s="46" t="s">
+      <c r="Y3" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="Z3" s="46" t="s">
+      <c r="Z3" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="AA3" s="73"/>
-      <c r="AB3" s="67" t="s">
+      <c r="AA3" s="63"/>
+      <c r="AB3" s="81" t="s">
         <v>80</v>
       </c>
-      <c r="AC3" s="68"/>
+      <c r="AC3" s="82"/>
       <c r="AD3" s="7" t="s">
         <v>13</v>
       </c>
@@ -1927,11 +1927,11 @@
       <c r="AG3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="AH3" s="73"/>
-      <c r="AI3" s="67" t="s">
+      <c r="AH3" s="63"/>
+      <c r="AI3" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="AJ3" s="68"/>
+      <c r="AJ3" s="82"/>
       <c r="AK3" s="7" t="s">
         <v>13</v>
       </c>
@@ -1944,7 +1944,7 @@
       <c r="AN3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="AO3" s="73"/>
+      <c r="AO3" s="63"/>
       <c r="AP3" s="7" t="s">
         <v>19</v>
       </c>
@@ -1957,7 +1957,7 @@
       <c r="AS3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="AT3" s="73"/>
+      <c r="AT3" s="63"/>
       <c r="AU3" s="7" t="s">
         <v>25</v>
       </c>
@@ -1991,7 +1991,7 @@
       <c r="BE3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="BF3" s="73"/>
+      <c r="BF3" s="63"/>
       <c r="BG3" s="11" t="s">
         <v>17</v>
       </c>
@@ -2004,14 +2004,14 @@
       <c r="BJ3" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="BK3" s="73"/>
-      <c r="BL3" s="47" t="s">
+      <c r="BK3" s="63"/>
+      <c r="BL3" s="46" t="s">
         <v>40</v>
       </c>
       <c r="BM3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="BN3" s="73"/>
+      <c r="BN3" s="63"/>
       <c r="BO3" s="7" t="s">
         <v>42</v>
       </c>
@@ -2057,10 +2057,10 @@
       <c r="CC3" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="CD3" s="38" t="s">
+      <c r="CD3" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="CE3" s="73"/>
+      <c r="CE3" s="63"/>
       <c r="CF3" s="7" t="s">
         <v>59</v>
       </c>
@@ -2076,7 +2076,7 @@
       <c r="CJ3" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="CK3" s="73"/>
+      <c r="CK3" s="63"/>
       <c r="CL3" s="11" t="s">
         <v>34</v>
       </c>
@@ -2086,74 +2086,74 @@
       <c r="CN3" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="CO3" s="73"/>
-      <c r="CP3" s="48" t="s">
+      <c r="CO3" s="63"/>
+      <c r="CP3" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="CQ3" s="48" t="s">
+      <c r="CQ3" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="CR3" s="48" t="s">
+      <c r="CR3" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="CS3" s="49" t="s">
+      <c r="CS3" s="48" t="s">
         <v>115</v>
       </c>
-      <c r="CT3" s="49" t="s">
+      <c r="CT3" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="CU3" s="48" t="s">
+      <c r="CU3" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="CV3" s="48" t="s">
+      <c r="CV3" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="CW3" s="50" t="s">
+      <c r="CW3" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="CX3" s="78"/>
-      <c r="CY3" s="50" t="s">
+      <c r="CX3" s="64"/>
+      <c r="CY3" s="49" t="s">
         <v>144</v>
       </c>
-      <c r="CZ3" s="50" t="s">
+      <c r="CZ3" s="49" t="s">
         <v>145</v>
       </c>
-      <c r="DA3" s="50" t="s">
+      <c r="DA3" s="49" t="s">
         <v>151</v>
       </c>
-      <c r="DB3" s="50" t="s">
+      <c r="DB3" s="49" t="s">
         <v>146</v>
       </c>
-      <c r="DC3" s="50" t="s">
+      <c r="DC3" s="49" t="s">
         <v>152</v>
       </c>
-      <c r="DD3" s="50" t="s">
+      <c r="DD3" s="49" t="s">
         <v>150</v>
       </c>
-      <c r="DE3" s="50" t="s">
+      <c r="DE3" s="49" t="s">
         <v>147</v>
       </c>
-      <c r="DF3" s="50" t="s">
+      <c r="DF3" s="49" t="s">
         <v>153</v>
       </c>
-      <c r="DG3" s="50" t="s">
+      <c r="DG3" s="49" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="4" spans="1:111" s="30" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="23">
+    <row r="4" spans="1:111" s="29" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22">
         <v>1</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>169</v>
+      <c r="B4" s="87" t="s">
+        <v>171</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="61">
+      <c r="E4" s="60">
         <v>41005</v>
       </c>
       <c r="F4" s="19" t="s">
@@ -2168,7 +2168,7 @@
       <c r="I4" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="J4" s="22" t="s">
+      <c r="J4" s="21" t="s">
         <v>121</v>
       </c>
       <c r="K4" s="2" t="s">
@@ -2184,7 +2184,7 @@
         <v>165</v>
       </c>
       <c r="O4" s="19"/>
-      <c r="P4" s="21" t="s">
+      <c r="P4" s="20" t="s">
         <v>122</v>
       </c>
       <c r="Q4" s="19" t="s">
@@ -2208,58 +2208,58 @@
       <c r="W4" s="17">
         <v>46298</v>
       </c>
-      <c r="X4" s="51" t="s">
+      <c r="X4" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="Y4" s="62" t="s">
+      <c r="Y4" s="61" t="s">
         <v>158</v>
       </c>
-      <c r="Z4" s="62" t="s">
+      <c r="Z4" s="61" t="s">
         <v>157</v>
       </c>
-      <c r="AA4" s="26"/>
-      <c r="AB4" s="21" t="s">
+      <c r="AA4" s="25"/>
+      <c r="AB4" s="20" t="s">
         <v>125</v>
       </c>
       <c r="AC4" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="AD4" s="21" t="s">
+      <c r="AD4" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="AE4" s="21" t="s">
+      <c r="AE4" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="AF4" s="21">
+      <c r="AF4" s="20">
         <v>390002</v>
       </c>
-      <c r="AG4" s="21" t="s">
+      <c r="AG4" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="AH4" s="26"/>
-      <c r="AI4" s="21" t="s">
+      <c r="AH4" s="25"/>
+      <c r="AI4" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="AJ4" s="21" t="s">
+      <c r="AJ4" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="AK4" s="21" t="s">
+      <c r="AK4" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="AL4" s="21" t="s">
+      <c r="AL4" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="AM4" s="21">
+      <c r="AM4" s="20">
         <v>390002</v>
       </c>
-      <c r="AN4" s="21" t="s">
+      <c r="AN4" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="AO4" s="26"/>
-      <c r="AP4" s="27">
+      <c r="AO4" s="25"/>
+      <c r="AP4" s="26">
         <v>9904969308</v>
       </c>
-      <c r="AQ4" s="27">
+      <c r="AQ4" s="26">
         <v>9924421246</v>
       </c>
       <c r="AR4" s="2" t="s">
@@ -2268,23 +2268,23 @@
       <c r="AS4" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="AT4" s="26"/>
-      <c r="AU4" s="28">
+      <c r="AT4" s="25"/>
+      <c r="AU4" s="27">
         <v>912010025212586</v>
       </c>
-      <c r="AV4" s="28" t="s">
+      <c r="AV4" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="AW4" s="28" t="s">
+      <c r="AW4" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="AX4" s="28" t="s">
+      <c r="AX4" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="AY4" s="28" t="s">
+      <c r="AY4" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="AZ4" s="21" t="s">
+      <c r="AZ4" s="20" t="s">
         <v>132</v>
       </c>
       <c r="BA4" s="2" t="s">
@@ -2293,36 +2293,36 @@
       <c r="BB4" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="BC4" s="52">
+      <c r="BC4" s="51">
         <v>278262824369</v>
       </c>
       <c r="BD4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="BE4" s="53">
+      <c r="BE4" s="52">
         <v>100275240386</v>
       </c>
-      <c r="BF4" s="26"/>
-      <c r="BG4" s="21" t="s">
+      <c r="BF4" s="25"/>
+      <c r="BG4" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="BH4" s="27" t="s">
+      <c r="BH4" s="26" t="s">
         <v>97</v>
       </c>
       <c r="BI4" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="BJ4" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="BJ4" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="BK4" s="26"/>
+      <c r="BK4" s="25"/>
       <c r="BL4" s="18">
         <v>210412101</v>
       </c>
       <c r="BM4" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="BN4" s="26"/>
+      <c r="BN4" s="25"/>
       <c r="BO4" s="2">
         <v>3</v>
       </c>
@@ -2368,10 +2368,10 @@
       <c r="CC4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="CD4" s="54" t="s">
+      <c r="CD4" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="CE4" s="26"/>
+      <c r="CE4" s="25"/>
       <c r="CF4" s="2" t="s">
         <v>137</v>
       </c>
@@ -2381,22 +2381,22 @@
       <c r="CH4" s="2">
         <v>9824846337</v>
       </c>
-      <c r="CI4" s="25" t="s">
+      <c r="CI4" s="24" t="s">
         <v>138</v>
       </c>
       <c r="CJ4" s="18"/>
-      <c r="CK4" s="26"/>
-      <c r="CL4" s="29"/>
-      <c r="CM4" s="29"/>
-      <c r="CN4" s="29"/>
-      <c r="CO4" s="26"/>
-      <c r="CP4" s="25" t="s">
+      <c r="CK4" s="25"/>
+      <c r="CL4" s="28"/>
+      <c r="CM4" s="28"/>
+      <c r="CN4" s="28"/>
+      <c r="CO4" s="25"/>
+      <c r="CP4" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="CQ4" s="25" t="s">
+      <c r="CQ4" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="CR4" s="25" t="s">
+      <c r="CR4" s="24" t="s">
         <v>65</v>
       </c>
       <c r="CS4" s="1">
@@ -2405,109 +2405,109 @@
       <c r="CT4" s="1">
         <v>1</v>
       </c>
-      <c r="CU4" s="25" t="s">
+      <c r="CU4" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="CV4" s="25" t="s">
+      <c r="CV4" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="CW4" s="25" t="s">
+      <c r="CW4" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="CX4" s="26"/>
-      <c r="CY4" s="25" t="s">
+      <c r="CX4" s="25"/>
+      <c r="CY4" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="CZ4" s="25"/>
-      <c r="DA4" s="25" t="s">
+      <c r="CZ4" s="24"/>
+      <c r="DA4" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="DB4" s="25" t="s">
+      <c r="DB4" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="DC4" s="60">
+      <c r="DC4" s="59">
         <v>41255</v>
       </c>
-      <c r="DD4" s="25" t="s">
+      <c r="DD4" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="DE4" s="25">
+      <c r="DE4" s="24">
         <v>1522</v>
       </c>
-      <c r="DF4" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="DG4" s="25" t="s">
+      <c r="DF4" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="DG4" s="24" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="5" spans="1:111" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:111" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="4"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="55"/>
+      <c r="E5" s="54"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="56"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="56"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="55"/>
+      <c r="N5" s="55"/>
+      <c r="O5" s="55"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
-      <c r="T5" s="55"/>
-      <c r="U5" s="55"/>
-      <c r="V5" s="55"/>
-      <c r="W5" s="55"/>
-      <c r="X5" s="55"/>
-      <c r="Y5" s="55"/>
-      <c r="Z5" s="55"/>
+      <c r="T5" s="54"/>
+      <c r="U5" s="54"/>
+      <c r="V5" s="54"/>
+      <c r="W5" s="54"/>
+      <c r="X5" s="54"/>
+      <c r="Y5" s="54"/>
+      <c r="Z5" s="54"/>
       <c r="AA5" s="3"/>
-      <c r="AB5" s="55"/>
-      <c r="AC5" s="55"/>
+      <c r="AB5" s="54"/>
+      <c r="AC5" s="54"/>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
       <c r="AG5" s="3"/>
       <c r="AH5" s="3"/>
-      <c r="AI5" s="55"/>
-      <c r="AJ5" s="55"/>
-      <c r="AK5" s="55"/>
+      <c r="AI5" s="54"/>
+      <c r="AJ5" s="54"/>
+      <c r="AK5" s="54"/>
       <c r="AL5" s="3"/>
       <c r="AM5" s="3"/>
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
       <c r="AP5" s="3"/>
       <c r="AQ5" s="3"/>
-      <c r="AR5" s="55"/>
+      <c r="AR5" s="54"/>
       <c r="AS5" s="3"/>
       <c r="AT5" s="3"/>
-      <c r="AU5" s="57"/>
+      <c r="AU5" s="56"/>
       <c r="AV5" s="5"/>
       <c r="AW5" s="5"/>
       <c r="AX5" s="3"/>
       <c r="AY5" s="3"/>
-      <c r="AZ5" s="58"/>
-      <c r="BA5" s="58"/>
+      <c r="AZ5" s="57"/>
+      <c r="BA5" s="57"/>
       <c r="BB5" s="3"/>
       <c r="BC5" s="3"/>
       <c r="BD5" s="3"/>
       <c r="BE5" s="3"/>
       <c r="BF5" s="3"/>
       <c r="BG5" s="3"/>
-      <c r="BH5" s="56"/>
-      <c r="BI5" s="56"/>
+      <c r="BH5" s="55"/>
+      <c r="BI5" s="55"/>
       <c r="BJ5" s="3"/>
-      <c r="BK5" s="56"/>
-      <c r="BL5" s="56"/>
-      <c r="BM5" s="56"/>
-      <c r="BN5" s="56"/>
+      <c r="BK5" s="55"/>
+      <c r="BL5" s="55"/>
+      <c r="BM5" s="55"/>
+      <c r="BN5" s="55"/>
       <c r="BO5" s="3"/>
       <c r="BP5" s="3"/>
       <c r="BQ5" s="3"/>
@@ -2525,11 +2525,11 @@
       <c r="CC5" s="3"/>
       <c r="CD5" s="3"/>
       <c r="CE5" s="3"/>
-      <c r="CF5" s="59"/>
+      <c r="CF5" s="58"/>
       <c r="CG5" s="3"/>
-      <c r="CH5" s="55"/>
-      <c r="CI5" s="55"/>
-      <c r="CJ5" s="56"/>
+      <c r="CH5" s="54"/>
+      <c r="CI5" s="54"/>
+      <c r="CJ5" s="55"/>
       <c r="CK5" s="3"/>
       <c r="CL5" s="3"/>
       <c r="CM5" s="3"/>
@@ -2550,73 +2550,73 @@
       <c r="DB5" s="3"/>
       <c r="DC5" s="3"/>
     </row>
-    <row r="6" spans="1:111" s="30" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:111" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="4"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="55"/>
+      <c r="E6" s="54"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="56"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="56"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="55"/>
+      <c r="M6" s="55"/>
+      <c r="N6" s="55"/>
+      <c r="O6" s="55"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="55"/>
-      <c r="U6" s="55"/>
-      <c r="V6" s="55"/>
-      <c r="W6" s="55"/>
-      <c r="X6" s="55"/>
-      <c r="Y6" s="55"/>
-      <c r="Z6" s="55"/>
+      <c r="T6" s="54"/>
+      <c r="U6" s="54"/>
+      <c r="V6" s="54"/>
+      <c r="W6" s="54"/>
+      <c r="X6" s="54"/>
+      <c r="Y6" s="54"/>
+      <c r="Z6" s="54"/>
       <c r="AA6" s="3"/>
-      <c r="AB6" s="55"/>
-      <c r="AC6" s="55"/>
+      <c r="AB6" s="54"/>
+      <c r="AC6" s="54"/>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
       <c r="AG6" s="3"/>
       <c r="AH6" s="3"/>
-      <c r="AI6" s="55"/>
-      <c r="AJ6" s="55"/>
-      <c r="AK6" s="55"/>
+      <c r="AI6" s="54"/>
+      <c r="AJ6" s="54"/>
+      <c r="AK6" s="54"/>
       <c r="AL6" s="3"/>
       <c r="AM6" s="3"/>
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
       <c r="AQ6" s="3"/>
-      <c r="AR6" s="55"/>
+      <c r="AR6" s="54"/>
       <c r="AS6" s="3"/>
       <c r="AT6" s="3"/>
-      <c r="AU6" s="57"/>
+      <c r="AU6" s="56"/>
       <c r="AV6" s="5"/>
       <c r="AW6" s="5"/>
       <c r="AX6" s="3"/>
       <c r="AY6" s="3"/>
-      <c r="AZ6" s="58"/>
-      <c r="BA6" s="58"/>
+      <c r="AZ6" s="57"/>
+      <c r="BA6" s="57"/>
       <c r="BB6" s="3"/>
       <c r="BC6" s="3"/>
       <c r="BD6" s="3"/>
       <c r="BE6" s="3"/>
       <c r="BF6" s="3"/>
       <c r="BG6" s="3"/>
-      <c r="BH6" s="56"/>
-      <c r="BI6" s="56"/>
+      <c r="BH6" s="55"/>
+      <c r="BI6" s="55"/>
       <c r="BJ6" s="3"/>
-      <c r="BK6" s="56"/>
-      <c r="BL6" s="56"/>
-      <c r="BM6" s="56"/>
-      <c r="BN6" s="56"/>
+      <c r="BK6" s="55"/>
+      <c r="BL6" s="55"/>
+      <c r="BM6" s="55"/>
+      <c r="BN6" s="55"/>
       <c r="BO6" s="3"/>
       <c r="BP6" s="3"/>
       <c r="BQ6" s="3"/>
@@ -2634,11 +2634,11 @@
       <c r="CC6" s="3"/>
       <c r="CD6" s="3"/>
       <c r="CE6" s="3"/>
-      <c r="CF6" s="59"/>
+      <c r="CF6" s="58"/>
       <c r="CG6" s="3"/>
-      <c r="CH6" s="55"/>
-      <c r="CI6" s="55"/>
-      <c r="CJ6" s="56"/>
+      <c r="CH6" s="54"/>
+      <c r="CI6" s="54"/>
+      <c r="CJ6" s="55"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
       <c r="CM6" s="3"/>
@@ -2659,73 +2659,73 @@
       <c r="DB6" s="3"/>
       <c r="DC6" s="3"/>
     </row>
-    <row r="7" spans="1:111" s="30" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:111" s="29" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="4"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="55"/>
+      <c r="E7" s="54"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="56"/>
-      <c r="O7" s="56"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="55"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="55"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="55"/>
-      <c r="U7" s="55"/>
-      <c r="V7" s="55"/>
-      <c r="W7" s="55"/>
-      <c r="X7" s="55"/>
-      <c r="Y7" s="55"/>
-      <c r="Z7" s="55"/>
+      <c r="T7" s="54"/>
+      <c r="U7" s="54"/>
+      <c r="V7" s="54"/>
+      <c r="W7" s="54"/>
+      <c r="X7" s="54"/>
+      <c r="Y7" s="54"/>
+      <c r="Z7" s="54"/>
       <c r="AA7" s="3"/>
-      <c r="AB7" s="55"/>
-      <c r="AC7" s="55"/>
+      <c r="AB7" s="54"/>
+      <c r="AC7" s="54"/>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3"/>
       <c r="AF7" s="3"/>
       <c r="AG7" s="3"/>
       <c r="AH7" s="3"/>
-      <c r="AI7" s="55"/>
-      <c r="AJ7" s="55"/>
-      <c r="AK7" s="55"/>
+      <c r="AI7" s="54"/>
+      <c r="AJ7" s="54"/>
+      <c r="AK7" s="54"/>
       <c r="AL7" s="3"/>
       <c r="AM7" s="3"/>
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
       <c r="AP7" s="3"/>
       <c r="AQ7" s="3"/>
-      <c r="AR7" s="55"/>
+      <c r="AR7" s="54"/>
       <c r="AS7" s="3"/>
       <c r="AT7" s="3"/>
-      <c r="AU7" s="57"/>
+      <c r="AU7" s="56"/>
       <c r="AV7" s="5"/>
       <c r="AW7" s="5"/>
       <c r="AX7" s="3"/>
       <c r="AY7" s="3"/>
-      <c r="AZ7" s="58"/>
-      <c r="BA7" s="58"/>
+      <c r="AZ7" s="57"/>
+      <c r="BA7" s="57"/>
       <c r="BB7" s="3"/>
       <c r="BC7" s="3"/>
       <c r="BD7" s="3"/>
       <c r="BE7" s="3"/>
       <c r="BF7" s="3"/>
       <c r="BG7" s="3"/>
-      <c r="BH7" s="56"/>
-      <c r="BI7" s="56"/>
+      <c r="BH7" s="55"/>
+      <c r="BI7" s="55"/>
       <c r="BJ7" s="3"/>
-      <c r="BK7" s="56"/>
-      <c r="BL7" s="56"/>
-      <c r="BM7" s="56"/>
-      <c r="BN7" s="56"/>
+      <c r="BK7" s="55"/>
+      <c r="BL7" s="55"/>
+      <c r="BM7" s="55"/>
+      <c r="BN7" s="55"/>
       <c r="BO7" s="3"/>
       <c r="BP7" s="3"/>
       <c r="BQ7" s="3"/>
@@ -2743,11 +2743,11 @@
       <c r="CC7" s="3"/>
       <c r="CD7" s="3"/>
       <c r="CE7" s="3"/>
-      <c r="CF7" s="59"/>
+      <c r="CF7" s="58"/>
       <c r="CG7" s="3"/>
-      <c r="CH7" s="55"/>
-      <c r="CI7" s="55"/>
-      <c r="CJ7" s="56"/>
+      <c r="CH7" s="54"/>
+      <c r="CI7" s="54"/>
+      <c r="CJ7" s="55"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
       <c r="CM7" s="3"/>
@@ -2768,73 +2768,73 @@
       <c r="DB7" s="3"/>
       <c r="DC7" s="3"/>
     </row>
-    <row r="8" spans="1:111" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:111" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="4"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
-      <c r="E8" s="55"/>
+      <c r="E8" s="54"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="55"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="56"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="56"/>
-      <c r="O8" s="56"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="54"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="55"/>
+      <c r="N8" s="55"/>
+      <c r="O8" s="55"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
-      <c r="T8" s="55"/>
-      <c r="U8" s="55"/>
-      <c r="V8" s="55"/>
-      <c r="W8" s="55"/>
-      <c r="X8" s="55"/>
-      <c r="Y8" s="55"/>
-      <c r="Z8" s="55"/>
+      <c r="T8" s="54"/>
+      <c r="U8" s="54"/>
+      <c r="V8" s="54"/>
+      <c r="W8" s="54"/>
+      <c r="X8" s="54"/>
+      <c r="Y8" s="54"/>
+      <c r="Z8" s="54"/>
       <c r="AA8" s="3"/>
-      <c r="AB8" s="55"/>
-      <c r="AC8" s="55"/>
+      <c r="AB8" s="54"/>
+      <c r="AC8" s="54"/>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3"/>
       <c r="AF8" s="3"/>
       <c r="AG8" s="3"/>
       <c r="AH8" s="3"/>
-      <c r="AI8" s="55"/>
-      <c r="AJ8" s="55"/>
-      <c r="AK8" s="55"/>
+      <c r="AI8" s="54"/>
+      <c r="AJ8" s="54"/>
+      <c r="AK8" s="54"/>
       <c r="AL8" s="3"/>
       <c r="AM8" s="3"/>
       <c r="AN8" s="3"/>
       <c r="AO8" s="3"/>
       <c r="AP8" s="3"/>
       <c r="AQ8" s="3"/>
-      <c r="AR8" s="55"/>
+      <c r="AR8" s="54"/>
       <c r="AS8" s="3"/>
       <c r="AT8" s="3"/>
-      <c r="AU8" s="57"/>
+      <c r="AU8" s="56"/>
       <c r="AV8" s="5"/>
       <c r="AW8" s="5"/>
       <c r="AX8" s="3"/>
       <c r="AY8" s="3"/>
-      <c r="AZ8" s="58"/>
-      <c r="BA8" s="58"/>
+      <c r="AZ8" s="57"/>
+      <c r="BA8" s="57"/>
       <c r="BB8" s="3"/>
       <c r="BC8" s="3"/>
       <c r="BD8" s="3"/>
       <c r="BE8" s="3"/>
       <c r="BF8" s="3"/>
       <c r="BG8" s="3"/>
-      <c r="BH8" s="56"/>
-      <c r="BI8" s="56"/>
+      <c r="BH8" s="55"/>
+      <c r="BI8" s="55"/>
       <c r="BJ8" s="3"/>
-      <c r="BK8" s="56"/>
-      <c r="BL8" s="56"/>
-      <c r="BM8" s="56"/>
-      <c r="BN8" s="56"/>
+      <c r="BK8" s="55"/>
+      <c r="BL8" s="55"/>
+      <c r="BM8" s="55"/>
+      <c r="BN8" s="55"/>
       <c r="BO8" s="3"/>
       <c r="BP8" s="3"/>
       <c r="BQ8" s="3"/>
@@ -2852,11 +2852,11 @@
       <c r="CC8" s="3"/>
       <c r="CD8" s="3"/>
       <c r="CE8" s="3"/>
-      <c r="CF8" s="59"/>
+      <c r="CF8" s="58"/>
       <c r="CG8" s="3"/>
-      <c r="CH8" s="55"/>
-      <c r="CI8" s="55"/>
-      <c r="CJ8" s="56"/>
+      <c r="CH8" s="54"/>
+      <c r="CI8" s="54"/>
+      <c r="CJ8" s="55"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
       <c r="CM8" s="3"/>
@@ -2877,73 +2877,73 @@
       <c r="DB8" s="3"/>
       <c r="DC8" s="3"/>
     </row>
-    <row r="9" spans="1:111" s="30" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:111" s="29" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="4"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
-      <c r="E9" s="55"/>
+      <c r="E9" s="54"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="55"/>
-      <c r="K9" s="55"/>
-      <c r="L9" s="56"/>
-      <c r="M9" s="56"/>
-      <c r="N9" s="56"/>
-      <c r="O9" s="56"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="54"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="55"/>
+      <c r="N9" s="55"/>
+      <c r="O9" s="55"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
-      <c r="T9" s="55"/>
-      <c r="U9" s="55"/>
-      <c r="V9" s="55"/>
-      <c r="W9" s="55"/>
-      <c r="X9" s="55"/>
-      <c r="Y9" s="55"/>
-      <c r="Z9" s="55"/>
+      <c r="T9" s="54"/>
+      <c r="U9" s="54"/>
+      <c r="V9" s="54"/>
+      <c r="W9" s="54"/>
+      <c r="X9" s="54"/>
+      <c r="Y9" s="54"/>
+      <c r="Z9" s="54"/>
       <c r="AA9" s="3"/>
-      <c r="AB9" s="55"/>
-      <c r="AC9" s="55"/>
+      <c r="AB9" s="54"/>
+      <c r="AC9" s="54"/>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3"/>
       <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
-      <c r="AI9" s="55"/>
-      <c r="AJ9" s="55"/>
-      <c r="AK9" s="55"/>
+      <c r="AI9" s="54"/>
+      <c r="AJ9" s="54"/>
+      <c r="AK9" s="54"/>
       <c r="AL9" s="3"/>
       <c r="AM9" s="3"/>
       <c r="AN9" s="3"/>
       <c r="AO9" s="3"/>
       <c r="AP9" s="3"/>
       <c r="AQ9" s="3"/>
-      <c r="AR9" s="55"/>
+      <c r="AR9" s="54"/>
       <c r="AS9" s="3"/>
       <c r="AT9" s="3"/>
-      <c r="AU9" s="57"/>
+      <c r="AU9" s="56"/>
       <c r="AV9" s="5"/>
       <c r="AW9" s="5"/>
       <c r="AX9" s="3"/>
       <c r="AY9" s="3"/>
-      <c r="AZ9" s="58"/>
-      <c r="BA9" s="58"/>
+      <c r="AZ9" s="57"/>
+      <c r="BA9" s="57"/>
       <c r="BB9" s="3"/>
       <c r="BC9" s="3"/>
       <c r="BD9" s="3"/>
       <c r="BE9" s="3"/>
       <c r="BF9" s="3"/>
       <c r="BG9" s="3"/>
-      <c r="BH9" s="56"/>
-      <c r="BI9" s="56"/>
+      <c r="BH9" s="55"/>
+      <c r="BI9" s="55"/>
       <c r="BJ9" s="3"/>
-      <c r="BK9" s="56"/>
-      <c r="BL9" s="56"/>
-      <c r="BM9" s="56"/>
-      <c r="BN9" s="56"/>
+      <c r="BK9" s="55"/>
+      <c r="BL9" s="55"/>
+      <c r="BM9" s="55"/>
+      <c r="BN9" s="55"/>
       <c r="BO9" s="3"/>
       <c r="BP9" s="3"/>
       <c r="BQ9" s="3"/>
@@ -2961,11 +2961,11 @@
       <c r="CC9" s="3"/>
       <c r="CD9" s="3"/>
       <c r="CE9" s="3"/>
-      <c r="CF9" s="59"/>
+      <c r="CF9" s="58"/>
       <c r="CG9" s="3"/>
-      <c r="CH9" s="55"/>
-      <c r="CI9" s="55"/>
-      <c r="CJ9" s="56"/>
+      <c r="CH9" s="54"/>
+      <c r="CI9" s="54"/>
+      <c r="CJ9" s="55"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
       <c r="CM9" s="3"/>
@@ -2986,73 +2986,73 @@
       <c r="DB9" s="3"/>
       <c r="DC9" s="3"/>
     </row>
-    <row r="10" spans="1:111" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:111" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="4"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
-      <c r="E10" s="55"/>
+      <c r="E10" s="54"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="55"/>
-      <c r="K10" s="55"/>
-      <c r="L10" s="56"/>
-      <c r="M10" s="56"/>
-      <c r="N10" s="56"/>
-      <c r="O10" s="56"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="54"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="55"/>
+      <c r="N10" s="55"/>
+      <c r="O10" s="55"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
-      <c r="T10" s="55"/>
-      <c r="U10" s="55"/>
-      <c r="V10" s="55"/>
-      <c r="W10" s="55"/>
-      <c r="X10" s="55"/>
-      <c r="Y10" s="55"/>
-      <c r="Z10" s="55"/>
+      <c r="T10" s="54"/>
+      <c r="U10" s="54"/>
+      <c r="V10" s="54"/>
+      <c r="W10" s="54"/>
+      <c r="X10" s="54"/>
+      <c r="Y10" s="54"/>
+      <c r="Z10" s="54"/>
       <c r="AA10" s="3"/>
-      <c r="AB10" s="55"/>
-      <c r="AC10" s="55"/>
+      <c r="AB10" s="54"/>
+      <c r="AC10" s="54"/>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3"/>
       <c r="AF10" s="3"/>
       <c r="AG10" s="3"/>
       <c r="AH10" s="3"/>
-      <c r="AI10" s="55"/>
-      <c r="AJ10" s="55"/>
-      <c r="AK10" s="55"/>
+      <c r="AI10" s="54"/>
+      <c r="AJ10" s="54"/>
+      <c r="AK10" s="54"/>
       <c r="AL10" s="3"/>
       <c r="AM10" s="3"/>
       <c r="AN10" s="3"/>
       <c r="AO10" s="3"/>
       <c r="AP10" s="3"/>
       <c r="AQ10" s="3"/>
-      <c r="AR10" s="55"/>
+      <c r="AR10" s="54"/>
       <c r="AS10" s="3"/>
       <c r="AT10" s="3"/>
-      <c r="AU10" s="57"/>
+      <c r="AU10" s="56"/>
       <c r="AV10" s="5"/>
       <c r="AW10" s="5"/>
       <c r="AX10" s="3"/>
       <c r="AY10" s="3"/>
-      <c r="AZ10" s="58"/>
-      <c r="BA10" s="58"/>
+      <c r="AZ10" s="57"/>
+      <c r="BA10" s="57"/>
       <c r="BB10" s="3"/>
       <c r="BC10" s="3"/>
       <c r="BD10" s="3"/>
       <c r="BE10" s="3"/>
       <c r="BF10" s="3"/>
       <c r="BG10" s="3"/>
-      <c r="BH10" s="56"/>
-      <c r="BI10" s="56"/>
+      <c r="BH10" s="55"/>
+      <c r="BI10" s="55"/>
       <c r="BJ10" s="3"/>
-      <c r="BK10" s="56"/>
-      <c r="BL10" s="56"/>
-      <c r="BM10" s="56"/>
-      <c r="BN10" s="56"/>
+      <c r="BK10" s="55"/>
+      <c r="BL10" s="55"/>
+      <c r="BM10" s="55"/>
+      <c r="BN10" s="55"/>
       <c r="BO10" s="3"/>
       <c r="BP10" s="3"/>
       <c r="BQ10" s="3"/>
@@ -3070,11 +3070,11 @@
       <c r="CC10" s="3"/>
       <c r="CD10" s="3"/>
       <c r="CE10" s="3"/>
-      <c r="CF10" s="59"/>
+      <c r="CF10" s="58"/>
       <c r="CG10" s="3"/>
-      <c r="CH10" s="55"/>
-      <c r="CI10" s="55"/>
-      <c r="CJ10" s="56"/>
+      <c r="CH10" s="54"/>
+      <c r="CI10" s="54"/>
+      <c r="CJ10" s="55"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
       <c r="CM10" s="3"/>
@@ -3095,73 +3095,73 @@
       <c r="DB10" s="3"/>
       <c r="DC10" s="3"/>
     </row>
-    <row r="11" spans="1:111" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:111" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="4"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
-      <c r="E11" s="55"/>
+      <c r="E11" s="54"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="56"/>
-      <c r="I11" s="56"/>
-      <c r="J11" s="55"/>
-      <c r="K11" s="55"/>
-      <c r="L11" s="56"/>
-      <c r="M11" s="56"/>
-      <c r="N11" s="56"/>
-      <c r="O11" s="56"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="55"/>
+      <c r="M11" s="55"/>
+      <c r="N11" s="55"/>
+      <c r="O11" s="55"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-      <c r="T11" s="55"/>
-      <c r="U11" s="55"/>
-      <c r="V11" s="55"/>
-      <c r="W11" s="55"/>
-      <c r="X11" s="55"/>
-      <c r="Y11" s="55"/>
-      <c r="Z11" s="55"/>
+      <c r="T11" s="54"/>
+      <c r="U11" s="54"/>
+      <c r="V11" s="54"/>
+      <c r="W11" s="54"/>
+      <c r="X11" s="54"/>
+      <c r="Y11" s="54"/>
+      <c r="Z11" s="54"/>
       <c r="AA11" s="3"/>
-      <c r="AB11" s="55"/>
-      <c r="AC11" s="55"/>
+      <c r="AB11" s="54"/>
+      <c r="AC11" s="54"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-      <c r="AI11" s="55"/>
-      <c r="AJ11" s="55"/>
-      <c r="AK11" s="55"/>
+      <c r="AI11" s="54"/>
+      <c r="AJ11" s="54"/>
+      <c r="AK11" s="54"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
       <c r="AQ11" s="3"/>
-      <c r="AR11" s="55"/>
+      <c r="AR11" s="54"/>
       <c r="AS11" s="3"/>
       <c r="AT11" s="3"/>
-      <c r="AU11" s="57"/>
+      <c r="AU11" s="56"/>
       <c r="AV11" s="5"/>
       <c r="AW11" s="5"/>
       <c r="AX11" s="3"/>
       <c r="AY11" s="3"/>
-      <c r="AZ11" s="58"/>
-      <c r="BA11" s="58"/>
+      <c r="AZ11" s="57"/>
+      <c r="BA11" s="57"/>
       <c r="BB11" s="3"/>
       <c r="BC11" s="3"/>
       <c r="BD11" s="3"/>
       <c r="BE11" s="3"/>
       <c r="BF11" s="3"/>
       <c r="BG11" s="3"/>
-      <c r="BH11" s="56"/>
-      <c r="BI11" s="56"/>
+      <c r="BH11" s="55"/>
+      <c r="BI11" s="55"/>
       <c r="BJ11" s="3"/>
-      <c r="BK11" s="56"/>
-      <c r="BL11" s="56"/>
-      <c r="BM11" s="56"/>
-      <c r="BN11" s="56"/>
+      <c r="BK11" s="55"/>
+      <c r="BL11" s="55"/>
+      <c r="BM11" s="55"/>
+      <c r="BN11" s="55"/>
       <c r="BO11" s="3"/>
       <c r="BP11" s="3"/>
       <c r="BQ11" s="3"/>
@@ -3179,11 +3179,11 @@
       <c r="CC11" s="3"/>
       <c r="CD11" s="3"/>
       <c r="CE11" s="3"/>
-      <c r="CF11" s="59"/>
+      <c r="CF11" s="58"/>
       <c r="CG11" s="3"/>
-      <c r="CH11" s="55"/>
-      <c r="CI11" s="55"/>
-      <c r="CJ11" s="56"/>
+      <c r="CH11" s="54"/>
+      <c r="CI11" s="54"/>
+      <c r="CJ11" s="55"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
       <c r="CM11" s="3"/>
@@ -3204,73 +3204,73 @@
       <c r="DB11" s="3"/>
       <c r="DC11" s="3"/>
     </row>
-    <row r="12" spans="1:111" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:111" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="4"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
-      <c r="E12" s="55"/>
+      <c r="E12" s="54"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="55"/>
-      <c r="K12" s="55"/>
-      <c r="L12" s="56"/>
-      <c r="M12" s="56"/>
-      <c r="N12" s="56"/>
-      <c r="O12" s="56"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="54"/>
+      <c r="K12" s="54"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="55"/>
+      <c r="N12" s="55"/>
+      <c r="O12" s="55"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
-      <c r="T12" s="55"/>
-      <c r="U12" s="55"/>
-      <c r="V12" s="55"/>
-      <c r="W12" s="55"/>
-      <c r="X12" s="55"/>
-      <c r="Y12" s="55"/>
-      <c r="Z12" s="55"/>
+      <c r="T12" s="54"/>
+      <c r="U12" s="54"/>
+      <c r="V12" s="54"/>
+      <c r="W12" s="54"/>
+      <c r="X12" s="54"/>
+      <c r="Y12" s="54"/>
+      <c r="Z12" s="54"/>
       <c r="AA12" s="3"/>
-      <c r="AB12" s="55"/>
-      <c r="AC12" s="55"/>
+      <c r="AB12" s="54"/>
+      <c r="AC12" s="54"/>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3"/>
       <c r="AF12" s="3"/>
       <c r="AG12" s="3"/>
       <c r="AH12" s="3"/>
-      <c r="AI12" s="55"/>
-      <c r="AJ12" s="55"/>
-      <c r="AK12" s="55"/>
+      <c r="AI12" s="54"/>
+      <c r="AJ12" s="54"/>
+      <c r="AK12" s="54"/>
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
       <c r="AN12" s="3"/>
       <c r="AO12" s="3"/>
       <c r="AP12" s="3"/>
       <c r="AQ12" s="3"/>
-      <c r="AR12" s="55"/>
+      <c r="AR12" s="54"/>
       <c r="AS12" s="3"/>
       <c r="AT12" s="3"/>
-      <c r="AU12" s="57"/>
+      <c r="AU12" s="56"/>
       <c r="AV12" s="5"/>
       <c r="AW12" s="5"/>
       <c r="AX12" s="3"/>
       <c r="AY12" s="3"/>
-      <c r="AZ12" s="58"/>
-      <c r="BA12" s="58"/>
+      <c r="AZ12" s="57"/>
+      <c r="BA12" s="57"/>
       <c r="BB12" s="3"/>
       <c r="BC12" s="3"/>
       <c r="BD12" s="3"/>
       <c r="BE12" s="3"/>
       <c r="BF12" s="3"/>
       <c r="BG12" s="3"/>
-      <c r="BH12" s="56"/>
-      <c r="BI12" s="56"/>
+      <c r="BH12" s="55"/>
+      <c r="BI12" s="55"/>
       <c r="BJ12" s="3"/>
-      <c r="BK12" s="56"/>
-      <c r="BL12" s="56"/>
-      <c r="BM12" s="56"/>
-      <c r="BN12" s="56"/>
+      <c r="BK12" s="55"/>
+      <c r="BL12" s="55"/>
+      <c r="BM12" s="55"/>
+      <c r="BN12" s="55"/>
       <c r="BO12" s="3"/>
       <c r="BP12" s="3"/>
       <c r="BQ12" s="3"/>
@@ -3288,11 +3288,11 @@
       <c r="CC12" s="3"/>
       <c r="CD12" s="3"/>
       <c r="CE12" s="3"/>
-      <c r="CF12" s="59"/>
+      <c r="CF12" s="58"/>
       <c r="CG12" s="3"/>
-      <c r="CH12" s="55"/>
-      <c r="CI12" s="55"/>
-      <c r="CJ12" s="56"/>
+      <c r="CH12" s="54"/>
+      <c r="CI12" s="54"/>
+      <c r="CJ12" s="55"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
       <c r="CM12" s="3"/>
@@ -3313,73 +3313,73 @@
       <c r="DB12" s="3"/>
       <c r="DC12" s="3"/>
     </row>
-    <row r="13" spans="1:111" s="30" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:111" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="4"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
-      <c r="E13" s="55"/>
+      <c r="E13" s="54"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="55"/>
-      <c r="K13" s="55"/>
-      <c r="L13" s="56"/>
-      <c r="M13" s="56"/>
-      <c r="N13" s="56"/>
-      <c r="O13" s="56"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="54"/>
+      <c r="K13" s="54"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="55"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="55"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
-      <c r="T13" s="55"/>
-      <c r="U13" s="55"/>
-      <c r="V13" s="55"/>
-      <c r="W13" s="55"/>
-      <c r="X13" s="55"/>
-      <c r="Y13" s="55"/>
-      <c r="Z13" s="55"/>
+      <c r="T13" s="54"/>
+      <c r="U13" s="54"/>
+      <c r="V13" s="54"/>
+      <c r="W13" s="54"/>
+      <c r="X13" s="54"/>
+      <c r="Y13" s="54"/>
+      <c r="Z13" s="54"/>
       <c r="AA13" s="3"/>
-      <c r="AB13" s="55"/>
-      <c r="AC13" s="55"/>
+      <c r="AB13" s="54"/>
+      <c r="AC13" s="54"/>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3"/>
       <c r="AF13" s="3"/>
       <c r="AG13" s="3"/>
       <c r="AH13" s="3"/>
-      <c r="AI13" s="55"/>
-      <c r="AJ13" s="55"/>
-      <c r="AK13" s="55"/>
+      <c r="AI13" s="54"/>
+      <c r="AJ13" s="54"/>
+      <c r="AK13" s="54"/>
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
       <c r="AN13" s="3"/>
       <c r="AO13" s="3"/>
       <c r="AP13" s="3"/>
       <c r="AQ13" s="3"/>
-      <c r="AR13" s="55"/>
+      <c r="AR13" s="54"/>
       <c r="AS13" s="3"/>
       <c r="AT13" s="3"/>
-      <c r="AU13" s="57"/>
+      <c r="AU13" s="56"/>
       <c r="AV13" s="5"/>
       <c r="AW13" s="5"/>
       <c r="AX13" s="3"/>
       <c r="AY13" s="3"/>
-      <c r="AZ13" s="58"/>
-      <c r="BA13" s="58"/>
+      <c r="AZ13" s="57"/>
+      <c r="BA13" s="57"/>
       <c r="BB13" s="3"/>
       <c r="BC13" s="3"/>
       <c r="BD13" s="3"/>
       <c r="BE13" s="3"/>
       <c r="BF13" s="3"/>
       <c r="BG13" s="3"/>
-      <c r="BH13" s="56"/>
-      <c r="BI13" s="56"/>
+      <c r="BH13" s="55"/>
+      <c r="BI13" s="55"/>
       <c r="BJ13" s="3"/>
-      <c r="BK13" s="56"/>
-      <c r="BL13" s="56"/>
-      <c r="BM13" s="56"/>
-      <c r="BN13" s="56"/>
+      <c r="BK13" s="55"/>
+      <c r="BL13" s="55"/>
+      <c r="BM13" s="55"/>
+      <c r="BN13" s="55"/>
       <c r="BO13" s="3"/>
       <c r="BP13" s="3"/>
       <c r="BQ13" s="3"/>
@@ -3397,11 +3397,11 @@
       <c r="CC13" s="3"/>
       <c r="CD13" s="3"/>
       <c r="CE13" s="3"/>
-      <c r="CF13" s="59"/>
+      <c r="CF13" s="58"/>
       <c r="CG13" s="3"/>
-      <c r="CH13" s="55"/>
-      <c r="CI13" s="55"/>
-      <c r="CJ13" s="56"/>
+      <c r="CH13" s="54"/>
+      <c r="CI13" s="54"/>
+      <c r="CJ13" s="55"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
       <c r="CM13" s="3"/>
@@ -3422,73 +3422,73 @@
       <c r="DB13" s="3"/>
       <c r="DC13" s="3"/>
     </row>
-    <row r="14" spans="1:111" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:111" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="4"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
-      <c r="E14" s="55"/>
+      <c r="E14" s="54"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="56"/>
-      <c r="J14" s="55"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="56"/>
-      <c r="M14" s="56"/>
-      <c r="N14" s="56"/>
-      <c r="O14" s="56"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="54"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="55"/>
+      <c r="N14" s="55"/>
+      <c r="O14" s="55"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
-      <c r="T14" s="55"/>
-      <c r="U14" s="55"/>
-      <c r="V14" s="55"/>
-      <c r="W14" s="55"/>
-      <c r="X14" s="55"/>
-      <c r="Y14" s="55"/>
-      <c r="Z14" s="55"/>
+      <c r="T14" s="54"/>
+      <c r="U14" s="54"/>
+      <c r="V14" s="54"/>
+      <c r="W14" s="54"/>
+      <c r="X14" s="54"/>
+      <c r="Y14" s="54"/>
+      <c r="Z14" s="54"/>
       <c r="AA14" s="3"/>
-      <c r="AB14" s="55"/>
-      <c r="AC14" s="55"/>
+      <c r="AB14" s="54"/>
+      <c r="AC14" s="54"/>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
       <c r="AG14" s="3"/>
       <c r="AH14" s="3"/>
-      <c r="AI14" s="55"/>
-      <c r="AJ14" s="55"/>
-      <c r="AK14" s="55"/>
+      <c r="AI14" s="54"/>
+      <c r="AJ14" s="54"/>
+      <c r="AK14" s="54"/>
       <c r="AL14" s="3"/>
       <c r="AM14" s="3"/>
       <c r="AN14" s="3"/>
       <c r="AO14" s="3"/>
       <c r="AP14" s="3"/>
       <c r="AQ14" s="3"/>
-      <c r="AR14" s="55"/>
+      <c r="AR14" s="54"/>
       <c r="AS14" s="3"/>
       <c r="AT14" s="3"/>
-      <c r="AU14" s="57"/>
+      <c r="AU14" s="56"/>
       <c r="AV14" s="5"/>
       <c r="AW14" s="5"/>
       <c r="AX14" s="3"/>
       <c r="AY14" s="3"/>
-      <c r="AZ14" s="58"/>
-      <c r="BA14" s="58"/>
+      <c r="AZ14" s="57"/>
+      <c r="BA14" s="57"/>
       <c r="BB14" s="3"/>
       <c r="BC14" s="3"/>
       <c r="BD14" s="3"/>
       <c r="BE14" s="3"/>
       <c r="BF14" s="3"/>
       <c r="BG14" s="3"/>
-      <c r="BH14" s="56"/>
-      <c r="BI14" s="56"/>
+      <c r="BH14" s="55"/>
+      <c r="BI14" s="55"/>
       <c r="BJ14" s="3"/>
-      <c r="BK14" s="56"/>
-      <c r="BL14" s="56"/>
-      <c r="BM14" s="56"/>
-      <c r="BN14" s="56"/>
+      <c r="BK14" s="55"/>
+      <c r="BL14" s="55"/>
+      <c r="BM14" s="55"/>
+      <c r="BN14" s="55"/>
       <c r="BO14" s="3"/>
       <c r="BP14" s="3"/>
       <c r="BQ14" s="3"/>
@@ -3506,11 +3506,11 @@
       <c r="CC14" s="3"/>
       <c r="CD14" s="3"/>
       <c r="CE14" s="3"/>
-      <c r="CF14" s="59"/>
+      <c r="CF14" s="58"/>
       <c r="CG14" s="3"/>
-      <c r="CH14" s="55"/>
-      <c r="CI14" s="55"/>
-      <c r="CJ14" s="56"/>
+      <c r="CH14" s="54"/>
+      <c r="CI14" s="54"/>
+      <c r="CJ14" s="55"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
       <c r="CM14" s="3"/>
@@ -3532,23 +3532,23 @@
       <c r="DC14" s="3"/>
     </row>
     <row r="15" spans="1:111" x14ac:dyDescent="0.2">
-      <c r="BA15" s="58"/>
+      <c r="BA15" s="57"/>
       <c r="BB15" s="3"/>
       <c r="BC15" s="3"/>
       <c r="BD15" s="3"/>
       <c r="BE15" s="3"/>
-      <c r="BH15" s="56"/>
-      <c r="BI15" s="56"/>
-      <c r="BK15" s="56"/>
-      <c r="BN15" s="56"/>
+      <c r="BH15" s="55"/>
+      <c r="BI15" s="55"/>
+      <c r="BK15" s="55"/>
+      <c r="BN15" s="55"/>
       <c r="BO15" s="3"/>
       <c r="BP15" s="3"/>
       <c r="BQ15" s="3"/>
       <c r="BR15" s="3"/>
-      <c r="CF15" s="59"/>
-      <c r="CH15" s="55"/>
-      <c r="CI15" s="55"/>
-      <c r="CJ15" s="56"/>
+      <c r="CF15" s="58"/>
+      <c r="CH15" s="54"/>
+      <c r="CI15" s="54"/>
+      <c r="CJ15" s="55"/>
       <c r="CL15" s="3"/>
       <c r="CM15" s="3"/>
       <c r="CN15" s="3"/>
@@ -3558,23 +3558,23 @@
       <c r="CT15" s="3"/>
     </row>
     <row r="16" spans="1:111" x14ac:dyDescent="0.2">
-      <c r="BA16" s="58"/>
+      <c r="BA16" s="57"/>
       <c r="BB16" s="3"/>
       <c r="BC16" s="3"/>
       <c r="BD16" s="3"/>
       <c r="BE16" s="3"/>
-      <c r="BH16" s="56"/>
-      <c r="BI16" s="56"/>
-      <c r="BK16" s="56"/>
-      <c r="BN16" s="56"/>
+      <c r="BH16" s="55"/>
+      <c r="BI16" s="55"/>
+      <c r="BK16" s="55"/>
+      <c r="BN16" s="55"/>
       <c r="BO16" s="3"/>
       <c r="BP16" s="3"/>
       <c r="BQ16" s="3"/>
       <c r="BR16" s="3"/>
-      <c r="CF16" s="59"/>
-      <c r="CH16" s="55"/>
-      <c r="CI16" s="55"/>
-      <c r="CJ16" s="56"/>
+      <c r="CF16" s="58"/>
+      <c r="CH16" s="54"/>
+      <c r="CI16" s="54"/>
+      <c r="CJ16" s="55"/>
       <c r="CL16" s="3"/>
       <c r="CM16" s="3"/>
       <c r="CN16" s="3"/>
@@ -3584,23 +3584,23 @@
       <c r="CT16" s="3"/>
     </row>
     <row r="17" spans="53:98" x14ac:dyDescent="0.2">
-      <c r="BA17" s="58"/>
+      <c r="BA17" s="57"/>
       <c r="BB17" s="3"/>
       <c r="BC17" s="3"/>
       <c r="BD17" s="3"/>
       <c r="BE17" s="3"/>
-      <c r="BH17" s="56"/>
-      <c r="BI17" s="56"/>
-      <c r="BK17" s="56"/>
-      <c r="BN17" s="56"/>
+      <c r="BH17" s="55"/>
+      <c r="BI17" s="55"/>
+      <c r="BK17" s="55"/>
+      <c r="BN17" s="55"/>
       <c r="BO17" s="3"/>
       <c r="BP17" s="3"/>
       <c r="BQ17" s="3"/>
       <c r="BR17" s="3"/>
-      <c r="CF17" s="59"/>
-      <c r="CH17" s="55"/>
-      <c r="CI17" s="55"/>
-      <c r="CJ17" s="56"/>
+      <c r="CF17" s="58"/>
+      <c r="CH17" s="54"/>
+      <c r="CI17" s="54"/>
+      <c r="CJ17" s="55"/>
       <c r="CL17" s="3"/>
       <c r="CM17" s="3"/>
       <c r="CN17" s="3"/>
@@ -3610,23 +3610,23 @@
       <c r="CT17" s="3"/>
     </row>
     <row r="18" spans="53:98" x14ac:dyDescent="0.2">
-      <c r="BA18" s="58"/>
+      <c r="BA18" s="57"/>
       <c r="BB18" s="3"/>
       <c r="BC18" s="3"/>
       <c r="BD18" s="3"/>
       <c r="BE18" s="3"/>
-      <c r="BH18" s="56"/>
-      <c r="BI18" s="56"/>
-      <c r="BK18" s="56"/>
-      <c r="BN18" s="56"/>
+      <c r="BH18" s="55"/>
+      <c r="BI18" s="55"/>
+      <c r="BK18" s="55"/>
+      <c r="BN18" s="55"/>
       <c r="BO18" s="3"/>
       <c r="BP18" s="3"/>
       <c r="BQ18" s="3"/>
       <c r="BR18" s="3"/>
-      <c r="CF18" s="59"/>
-      <c r="CH18" s="55"/>
-      <c r="CI18" s="55"/>
-      <c r="CJ18" s="56"/>
+      <c r="CF18" s="58"/>
+      <c r="CH18" s="54"/>
+      <c r="CI18" s="54"/>
+      <c r="CJ18" s="55"/>
       <c r="CL18" s="3"/>
       <c r="CM18" s="3"/>
       <c r="CN18" s="3"/>
@@ -3636,23 +3636,23 @@
       <c r="CT18" s="3"/>
     </row>
     <row r="19" spans="53:98" x14ac:dyDescent="0.2">
-      <c r="BA19" s="58"/>
+      <c r="BA19" s="57"/>
       <c r="BB19" s="3"/>
       <c r="BC19" s="3"/>
       <c r="BD19" s="3"/>
       <c r="BE19" s="3"/>
-      <c r="BH19" s="56"/>
-      <c r="BI19" s="56"/>
-      <c r="BK19" s="56"/>
-      <c r="BN19" s="56"/>
+      <c r="BH19" s="55"/>
+      <c r="BI19" s="55"/>
+      <c r="BK19" s="55"/>
+      <c r="BN19" s="55"/>
       <c r="BO19" s="3"/>
       <c r="BP19" s="3"/>
       <c r="BQ19" s="3"/>
       <c r="BR19" s="3"/>
-      <c r="CF19" s="59"/>
-      <c r="CH19" s="55"/>
-      <c r="CI19" s="55"/>
-      <c r="CJ19" s="56"/>
+      <c r="CF19" s="58"/>
+      <c r="CH19" s="54"/>
+      <c r="CI19" s="54"/>
+      <c r="CJ19" s="55"/>
       <c r="CL19" s="3"/>
       <c r="CM19" s="3"/>
       <c r="CN19" s="3"/>
@@ -3662,23 +3662,23 @@
       <c r="CT19" s="3"/>
     </row>
     <row r="20" spans="53:98" x14ac:dyDescent="0.2">
-      <c r="BA20" s="58"/>
+      <c r="BA20" s="57"/>
       <c r="BB20" s="3"/>
       <c r="BC20" s="3"/>
       <c r="BD20" s="3"/>
       <c r="BE20" s="3"/>
-      <c r="BH20" s="56"/>
-      <c r="BI20" s="56"/>
-      <c r="BK20" s="56"/>
-      <c r="BN20" s="56"/>
+      <c r="BH20" s="55"/>
+      <c r="BI20" s="55"/>
+      <c r="BK20" s="55"/>
+      <c r="BN20" s="55"/>
       <c r="BO20" s="3"/>
       <c r="BP20" s="3"/>
       <c r="BQ20" s="3"/>
       <c r="BR20" s="3"/>
-      <c r="CF20" s="59"/>
-      <c r="CH20" s="55"/>
-      <c r="CI20" s="55"/>
-      <c r="CJ20" s="56"/>
+      <c r="CF20" s="58"/>
+      <c r="CH20" s="54"/>
+      <c r="CI20" s="54"/>
+      <c r="CJ20" s="55"/>
       <c r="CL20" s="3"/>
       <c r="CM20" s="3"/>
       <c r="CN20" s="3"/>
@@ -3688,23 +3688,23 @@
       <c r="CT20" s="3"/>
     </row>
     <row r="21" spans="53:98" x14ac:dyDescent="0.2">
-      <c r="BA21" s="58"/>
+      <c r="BA21" s="57"/>
       <c r="BB21" s="3"/>
       <c r="BC21" s="3"/>
       <c r="BD21" s="3"/>
       <c r="BE21" s="3"/>
-      <c r="BH21" s="56"/>
-      <c r="BI21" s="56"/>
-      <c r="BK21" s="56"/>
-      <c r="BN21" s="56"/>
+      <c r="BH21" s="55"/>
+      <c r="BI21" s="55"/>
+      <c r="BK21" s="55"/>
+      <c r="BN21" s="55"/>
       <c r="BO21" s="3"/>
       <c r="BP21" s="3"/>
       <c r="BQ21" s="3"/>
       <c r="BR21" s="3"/>
-      <c r="CF21" s="59"/>
-      <c r="CH21" s="55"/>
-      <c r="CI21" s="55"/>
-      <c r="CJ21" s="56"/>
+      <c r="CF21" s="58"/>
+      <c r="CH21" s="54"/>
+      <c r="CI21" s="54"/>
+      <c r="CJ21" s="55"/>
       <c r="CL21" s="3"/>
       <c r="CM21" s="3"/>
       <c r="CN21" s="3"/>
@@ -3714,23 +3714,23 @@
       <c r="CT21" s="3"/>
     </row>
     <row r="22" spans="53:98" x14ac:dyDescent="0.2">
-      <c r="BA22" s="58"/>
+      <c r="BA22" s="57"/>
       <c r="BB22" s="3"/>
       <c r="BC22" s="3"/>
       <c r="BD22" s="3"/>
       <c r="BE22" s="3"/>
-      <c r="BH22" s="56"/>
-      <c r="BI22" s="56"/>
-      <c r="BK22" s="56"/>
-      <c r="BN22" s="56"/>
+      <c r="BH22" s="55"/>
+      <c r="BI22" s="55"/>
+      <c r="BK22" s="55"/>
+      <c r="BN22" s="55"/>
       <c r="BO22" s="3"/>
       <c r="BP22" s="3"/>
       <c r="BQ22" s="3"/>
       <c r="BR22" s="3"/>
-      <c r="CF22" s="59"/>
-      <c r="CH22" s="55"/>
-      <c r="CI22" s="55"/>
-      <c r="CJ22" s="56"/>
+      <c r="CF22" s="58"/>
+      <c r="CH22" s="54"/>
+      <c r="CI22" s="54"/>
+      <c r="CJ22" s="55"/>
       <c r="CL22" s="3"/>
       <c r="CM22" s="3"/>
       <c r="CN22" s="3"/>
@@ -3740,23 +3740,23 @@
       <c r="CT22" s="3"/>
     </row>
     <row r="23" spans="53:98" x14ac:dyDescent="0.2">
-      <c r="BA23" s="58"/>
+      <c r="BA23" s="57"/>
       <c r="BB23" s="3"/>
       <c r="BC23" s="3"/>
       <c r="BD23" s="3"/>
       <c r="BE23" s="3"/>
-      <c r="BH23" s="56"/>
-      <c r="BI23" s="56"/>
-      <c r="BK23" s="56"/>
-      <c r="BN23" s="56"/>
+      <c r="BH23" s="55"/>
+      <c r="BI23" s="55"/>
+      <c r="BK23" s="55"/>
+      <c r="BN23" s="55"/>
       <c r="BO23" s="3"/>
       <c r="BP23" s="3"/>
       <c r="BQ23" s="3"/>
       <c r="BR23" s="3"/>
-      <c r="CF23" s="59"/>
-      <c r="CH23" s="55"/>
-      <c r="CI23" s="55"/>
-      <c r="CJ23" s="56"/>
+      <c r="CF23" s="58"/>
+      <c r="CH23" s="54"/>
+      <c r="CI23" s="54"/>
+      <c r="CJ23" s="55"/>
       <c r="CL23" s="3"/>
       <c r="CM23" s="3"/>
       <c r="CN23" s="3"/>
@@ -3766,23 +3766,23 @@
       <c r="CT23" s="3"/>
     </row>
     <row r="24" spans="53:98" x14ac:dyDescent="0.2">
-      <c r="BA24" s="58"/>
+      <c r="BA24" s="57"/>
       <c r="BB24" s="3"/>
       <c r="BC24" s="3"/>
       <c r="BD24" s="3"/>
       <c r="BE24" s="3"/>
-      <c r="BH24" s="56"/>
-      <c r="BI24" s="56"/>
-      <c r="BK24" s="56"/>
-      <c r="BN24" s="56"/>
+      <c r="BH24" s="55"/>
+      <c r="BI24" s="55"/>
+      <c r="BK24" s="55"/>
+      <c r="BN24" s="55"/>
       <c r="BO24" s="3"/>
       <c r="BP24" s="3"/>
       <c r="BQ24" s="3"/>
       <c r="BR24" s="3"/>
-      <c r="CF24" s="59"/>
-      <c r="CH24" s="55"/>
-      <c r="CI24" s="55"/>
-      <c r="CJ24" s="56"/>
+      <c r="CF24" s="58"/>
+      <c r="CH24" s="54"/>
+      <c r="CI24" s="54"/>
+      <c r="CJ24" s="55"/>
       <c r="CL24" s="3"/>
       <c r="CM24" s="3"/>
       <c r="CN24" s="3"/>
@@ -3792,23 +3792,23 @@
       <c r="CT24" s="3"/>
     </row>
     <row r="25" spans="53:98" x14ac:dyDescent="0.2">
-      <c r="BA25" s="58"/>
+      <c r="BA25" s="57"/>
       <c r="BB25" s="3"/>
       <c r="BC25" s="3"/>
       <c r="BD25" s="3"/>
       <c r="BE25" s="3"/>
-      <c r="BH25" s="56"/>
-      <c r="BI25" s="56"/>
-      <c r="BK25" s="56"/>
-      <c r="BN25" s="56"/>
+      <c r="BH25" s="55"/>
+      <c r="BI25" s="55"/>
+      <c r="BK25" s="55"/>
+      <c r="BN25" s="55"/>
       <c r="BO25" s="3"/>
       <c r="BP25" s="3"/>
       <c r="BQ25" s="3"/>
       <c r="BR25" s="3"/>
-      <c r="CF25" s="59"/>
-      <c r="CH25" s="55"/>
-      <c r="CI25" s="55"/>
-      <c r="CJ25" s="56"/>
+      <c r="CF25" s="58"/>
+      <c r="CH25" s="54"/>
+      <c r="CI25" s="54"/>
+      <c r="CJ25" s="55"/>
       <c r="CL25" s="3"/>
       <c r="CM25" s="3"/>
       <c r="CN25" s="3"/>
@@ -3818,23 +3818,23 @@
       <c r="CT25" s="3"/>
     </row>
     <row r="26" spans="53:98" x14ac:dyDescent="0.2">
-      <c r="BA26" s="58"/>
+      <c r="BA26" s="57"/>
       <c r="BB26" s="3"/>
       <c r="BC26" s="3"/>
       <c r="BD26" s="3"/>
       <c r="BE26" s="3"/>
-      <c r="BH26" s="56"/>
-      <c r="BI26" s="56"/>
-      <c r="BK26" s="56"/>
-      <c r="BN26" s="56"/>
+      <c r="BH26" s="55"/>
+      <c r="BI26" s="55"/>
+      <c r="BK26" s="55"/>
+      <c r="BN26" s="55"/>
       <c r="BO26" s="3"/>
       <c r="BP26" s="3"/>
       <c r="BQ26" s="3"/>
       <c r="BR26" s="3"/>
-      <c r="CF26" s="59"/>
-      <c r="CH26" s="55"/>
-      <c r="CI26" s="55"/>
-      <c r="CJ26" s="56"/>
+      <c r="CF26" s="58"/>
+      <c r="CH26" s="54"/>
+      <c r="CI26" s="54"/>
+      <c r="CJ26" s="55"/>
       <c r="CL26" s="3"/>
       <c r="CM26" s="3"/>
       <c r="CN26" s="3"/>
@@ -3844,23 +3844,23 @@
       <c r="CT26" s="3"/>
     </row>
     <row r="27" spans="53:98" x14ac:dyDescent="0.2">
-      <c r="BA27" s="58"/>
+      <c r="BA27" s="57"/>
       <c r="BB27" s="3"/>
       <c r="BC27" s="3"/>
       <c r="BD27" s="3"/>
       <c r="BE27" s="3"/>
-      <c r="BH27" s="56"/>
-      <c r="BI27" s="56"/>
-      <c r="BK27" s="56"/>
-      <c r="BN27" s="56"/>
+      <c r="BH27" s="55"/>
+      <c r="BI27" s="55"/>
+      <c r="BK27" s="55"/>
+      <c r="BN27" s="55"/>
       <c r="BO27" s="3"/>
       <c r="BP27" s="3"/>
       <c r="BQ27" s="3"/>
       <c r="BR27" s="3"/>
-      <c r="CF27" s="59"/>
-      <c r="CH27" s="55"/>
-      <c r="CI27" s="55"/>
-      <c r="CJ27" s="56"/>
+      <c r="CF27" s="58"/>
+      <c r="CH27" s="54"/>
+      <c r="CI27" s="54"/>
+      <c r="CJ27" s="55"/>
       <c r="CL27" s="3"/>
       <c r="CM27" s="3"/>
       <c r="CN27" s="3"/>
@@ -3870,23 +3870,23 @@
       <c r="CT27" s="3"/>
     </row>
     <row r="28" spans="53:98" x14ac:dyDescent="0.2">
-      <c r="BA28" s="58"/>
+      <c r="BA28" s="57"/>
       <c r="BB28" s="3"/>
       <c r="BC28" s="3"/>
       <c r="BD28" s="3"/>
       <c r="BE28" s="3"/>
-      <c r="BH28" s="56"/>
-      <c r="BI28" s="56"/>
-      <c r="BK28" s="56"/>
-      <c r="BN28" s="56"/>
+      <c r="BH28" s="55"/>
+      <c r="BI28" s="55"/>
+      <c r="BK28" s="55"/>
+      <c r="BN28" s="55"/>
       <c r="BO28" s="3"/>
       <c r="BP28" s="3"/>
       <c r="BQ28" s="3"/>
       <c r="BR28" s="3"/>
-      <c r="CF28" s="59"/>
-      <c r="CH28" s="55"/>
-      <c r="CI28" s="55"/>
-      <c r="CJ28" s="56"/>
+      <c r="CF28" s="58"/>
+      <c r="CH28" s="54"/>
+      <c r="CI28" s="54"/>
+      <c r="CJ28" s="55"/>
       <c r="CL28" s="3"/>
       <c r="CM28" s="3"/>
       <c r="CN28" s="3"/>
@@ -3896,23 +3896,23 @@
       <c r="CT28" s="3"/>
     </row>
     <row r="29" spans="53:98" x14ac:dyDescent="0.2">
-      <c r="BA29" s="58"/>
+      <c r="BA29" s="57"/>
       <c r="BB29" s="3"/>
       <c r="BC29" s="3"/>
       <c r="BD29" s="3"/>
       <c r="BE29" s="3"/>
-      <c r="BH29" s="56"/>
-      <c r="BI29" s="56"/>
-      <c r="BK29" s="56"/>
-      <c r="BN29" s="56"/>
+      <c r="BH29" s="55"/>
+      <c r="BI29" s="55"/>
+      <c r="BK29" s="55"/>
+      <c r="BN29" s="55"/>
       <c r="BO29" s="3"/>
       <c r="BP29" s="3"/>
       <c r="BQ29" s="3"/>
       <c r="BR29" s="3"/>
-      <c r="CF29" s="59"/>
-      <c r="CH29" s="55"/>
-      <c r="CI29" s="55"/>
-      <c r="CJ29" s="56"/>
+      <c r="CF29" s="58"/>
+      <c r="CH29" s="54"/>
+      <c r="CI29" s="54"/>
+      <c r="CJ29" s="55"/>
       <c r="CL29" s="3"/>
       <c r="CM29" s="3"/>
       <c r="CN29" s="3"/>
@@ -3922,23 +3922,23 @@
       <c r="CT29" s="3"/>
     </row>
     <row r="30" spans="53:98" x14ac:dyDescent="0.2">
-      <c r="BA30" s="58"/>
+      <c r="BA30" s="57"/>
       <c r="BB30" s="3"/>
       <c r="BC30" s="3"/>
       <c r="BD30" s="3"/>
       <c r="BE30" s="3"/>
-      <c r="BH30" s="56"/>
-      <c r="BI30" s="56"/>
-      <c r="BK30" s="56"/>
-      <c r="BN30" s="56"/>
+      <c r="BH30" s="55"/>
+      <c r="BI30" s="55"/>
+      <c r="BK30" s="55"/>
+      <c r="BN30" s="55"/>
       <c r="BO30" s="3"/>
       <c r="BP30" s="3"/>
       <c r="BQ30" s="3"/>
       <c r="BR30" s="3"/>
-      <c r="CF30" s="59"/>
-      <c r="CH30" s="55"/>
-      <c r="CI30" s="55"/>
-      <c r="CJ30" s="56"/>
+      <c r="CF30" s="58"/>
+      <c r="CH30" s="54"/>
+      <c r="CI30" s="54"/>
+      <c r="CJ30" s="55"/>
       <c r="CL30" s="3"/>
       <c r="CM30" s="3"/>
       <c r="CN30" s="3"/>
@@ -3948,23 +3948,23 @@
       <c r="CT30" s="3"/>
     </row>
     <row r="31" spans="53:98" x14ac:dyDescent="0.2">
-      <c r="BA31" s="58"/>
+      <c r="BA31" s="57"/>
       <c r="BB31" s="3"/>
       <c r="BC31" s="3"/>
       <c r="BD31" s="3"/>
       <c r="BE31" s="3"/>
-      <c r="BH31" s="56"/>
-      <c r="BI31" s="56"/>
-      <c r="BK31" s="56"/>
-      <c r="BN31" s="56"/>
+      <c r="BH31" s="55"/>
+      <c r="BI31" s="55"/>
+      <c r="BK31" s="55"/>
+      <c r="BN31" s="55"/>
       <c r="BO31" s="3"/>
       <c r="BP31" s="3"/>
       <c r="BQ31" s="3"/>
       <c r="BR31" s="3"/>
-      <c r="CF31" s="59"/>
-      <c r="CH31" s="55"/>
-      <c r="CI31" s="55"/>
-      <c r="CJ31" s="56"/>
+      <c r="CF31" s="58"/>
+      <c r="CH31" s="54"/>
+      <c r="CI31" s="54"/>
+      <c r="CJ31" s="55"/>
       <c r="CL31" s="3"/>
       <c r="CM31" s="3"/>
       <c r="CN31" s="3"/>
@@ -3974,23 +3974,23 @@
       <c r="CT31" s="3"/>
     </row>
     <row r="32" spans="53:98" x14ac:dyDescent="0.2">
-      <c r="BA32" s="58"/>
+      <c r="BA32" s="57"/>
       <c r="BB32" s="3"/>
       <c r="BC32" s="3"/>
       <c r="BD32" s="3"/>
       <c r="BE32" s="3"/>
-      <c r="BH32" s="56"/>
-      <c r="BI32" s="56"/>
-      <c r="BK32" s="56"/>
-      <c r="BN32" s="56"/>
+      <c r="BH32" s="55"/>
+      <c r="BI32" s="55"/>
+      <c r="BK32" s="55"/>
+      <c r="BN32" s="55"/>
       <c r="BO32" s="3"/>
       <c r="BP32" s="3"/>
       <c r="BQ32" s="3"/>
       <c r="BR32" s="3"/>
-      <c r="CF32" s="59"/>
-      <c r="CH32" s="55"/>
-      <c r="CI32" s="55"/>
-      <c r="CJ32" s="56"/>
+      <c r="CF32" s="58"/>
+      <c r="CH32" s="54"/>
+      <c r="CI32" s="54"/>
+      <c r="CJ32" s="55"/>
       <c r="CL32" s="3"/>
       <c r="CM32" s="3"/>
       <c r="CN32" s="3"/>
@@ -4000,23 +4000,23 @@
       <c r="CT32" s="3"/>
     </row>
     <row r="33" spans="53:98" x14ac:dyDescent="0.2">
-      <c r="BA33" s="58"/>
+      <c r="BA33" s="57"/>
       <c r="BB33" s="3"/>
       <c r="BC33" s="3"/>
       <c r="BD33" s="3"/>
       <c r="BE33" s="3"/>
-      <c r="BH33" s="56"/>
-      <c r="BI33" s="56"/>
-      <c r="BK33" s="56"/>
-      <c r="BN33" s="56"/>
+      <c r="BH33" s="55"/>
+      <c r="BI33" s="55"/>
+      <c r="BK33" s="55"/>
+      <c r="BN33" s="55"/>
       <c r="BO33" s="3"/>
       <c r="BP33" s="3"/>
       <c r="BQ33" s="3"/>
       <c r="BR33" s="3"/>
-      <c r="CF33" s="59"/>
-      <c r="CH33" s="55"/>
-      <c r="CI33" s="55"/>
-      <c r="CJ33" s="56"/>
+      <c r="CF33" s="58"/>
+      <c r="CH33" s="54"/>
+      <c r="CI33" s="54"/>
+      <c r="CJ33" s="55"/>
       <c r="CL33" s="3"/>
       <c r="CM33" s="3"/>
       <c r="CN33" s="3"/>
@@ -4026,23 +4026,23 @@
       <c r="CT33" s="3"/>
     </row>
     <row r="34" spans="53:98" x14ac:dyDescent="0.2">
-      <c r="BA34" s="58"/>
+      <c r="BA34" s="57"/>
       <c r="BB34" s="3"/>
       <c r="BC34" s="3"/>
       <c r="BD34" s="3"/>
       <c r="BE34" s="3"/>
-      <c r="BH34" s="56"/>
-      <c r="BI34" s="56"/>
-      <c r="BK34" s="56"/>
-      <c r="BN34" s="56"/>
+      <c r="BH34" s="55"/>
+      <c r="BI34" s="55"/>
+      <c r="BK34" s="55"/>
+      <c r="BN34" s="55"/>
       <c r="BO34" s="3"/>
       <c r="BP34" s="3"/>
       <c r="BQ34" s="3"/>
       <c r="BR34" s="3"/>
-      <c r="CF34" s="59"/>
-      <c r="CH34" s="55"/>
-      <c r="CI34" s="55"/>
-      <c r="CJ34" s="56"/>
+      <c r="CF34" s="58"/>
+      <c r="CH34" s="54"/>
+      <c r="CI34" s="54"/>
+      <c r="CJ34" s="55"/>
       <c r="CL34" s="3"/>
       <c r="CM34" s="3"/>
       <c r="CN34" s="3"/>
@@ -4052,23 +4052,23 @@
       <c r="CT34" s="3"/>
     </row>
     <row r="35" spans="53:98" x14ac:dyDescent="0.2">
-      <c r="BA35" s="58"/>
+      <c r="BA35" s="57"/>
       <c r="BB35" s="3"/>
       <c r="BC35" s="3"/>
       <c r="BD35" s="3"/>
       <c r="BE35" s="3"/>
-      <c r="BH35" s="56"/>
-      <c r="BI35" s="56"/>
-      <c r="BK35" s="56"/>
-      <c r="BN35" s="56"/>
+      <c r="BH35" s="55"/>
+      <c r="BI35" s="55"/>
+      <c r="BK35" s="55"/>
+      <c r="BN35" s="55"/>
       <c r="BO35" s="3"/>
       <c r="BP35" s="3"/>
       <c r="BQ35" s="3"/>
       <c r="BR35" s="3"/>
-      <c r="CF35" s="59"/>
-      <c r="CH35" s="55"/>
-      <c r="CI35" s="55"/>
-      <c r="CJ35" s="56"/>
+      <c r="CF35" s="58"/>
+      <c r="CH35" s="54"/>
+      <c r="CI35" s="54"/>
+      <c r="CJ35" s="55"/>
       <c r="CL35" s="3"/>
       <c r="CM35" s="3"/>
       <c r="CN35" s="3"/>
@@ -4082,6 +4082,18 @@
     <sortCondition ref="B4"/>
   </sortState>
   <mergeCells count="28">
+    <mergeCell ref="CF2:CJ2"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="CA1:CD1"/>
+    <mergeCell ref="CE1:CE3"/>
+    <mergeCell ref="CK1:CK3"/>
+    <mergeCell ref="AH1:AH3"/>
+    <mergeCell ref="AO1:AO3"/>
+    <mergeCell ref="AT1:AT3"/>
+    <mergeCell ref="AU1:BE1"/>
+    <mergeCell ref="BF1:BF3"/>
     <mergeCell ref="CO1:CO3"/>
     <mergeCell ref="CX1:CX3"/>
     <mergeCell ref="C2:D2"/>
@@ -4098,18 +4110,6 @@
     <mergeCell ref="BL2:BM2"/>
     <mergeCell ref="BO2:CD2"/>
     <mergeCell ref="AA1:AA3"/>
-    <mergeCell ref="CF2:CJ2"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="CA1:CD1"/>
-    <mergeCell ref="CE1:CE3"/>
-    <mergeCell ref="CK1:CK3"/>
-    <mergeCell ref="AH1:AH3"/>
-    <mergeCell ref="AO1:AO3"/>
-    <mergeCell ref="AT1:AT3"/>
-    <mergeCell ref="AU1:BE1"/>
-    <mergeCell ref="BF1:BF3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/web/src/main/webapp/StorageYard/Other/UserDoc/Payroll/Staff Info for HRMS Demo.xlsx
+++ b/web/src/main/webapp/StorageYard/Other/UserDoc/Payroll/Staff Info for HRMS Demo.xlsx
@@ -23,10 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="233">
-  <si>
-    <t>Team</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="232">
   <si>
     <t>Date of Joining</t>
   </si>
@@ -119,9 +116,6 @@
   </si>
   <si>
     <t>Final Leave Date</t>
-  </si>
-  <si>
-    <t>Sub - Team</t>
   </si>
   <si>
     <t>Line Manager</t>
@@ -366,9 +360,6 @@
     <t>Company</t>
   </si>
   <si>
-    <t>department</t>
-  </si>
-  <si>
     <t>General</t>
   </si>
   <si>
@@ -687,9 +678,6 @@
     <t>married</t>
   </si>
   <si>
-    <t>unarried</t>
-  </si>
-  <si>
     <t xml:space="preserve">Technical  </t>
   </si>
   <si>
@@ -724,6 +712,15 @@
   </si>
   <si>
     <t>A3</t>
+  </si>
+  <si>
+    <t>Business Unit</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Division</t>
   </si>
 </sst>
 </file>
@@ -1632,7 +1629,7 @@
   <sheetData>
     <row r="1" spans="1:110" s="36" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1660,7 +1657,7 @@
       <c r="Y1" s="11"/>
       <c r="Z1" s="11"/>
       <c r="AA1" s="51" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AB1" s="11"/>
       <c r="AC1" s="11"/>
@@ -1669,13 +1666,13 @@
       <c r="AF1" s="11"/>
       <c r="AG1" s="11"/>
       <c r="AH1" s="51" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AI1" s="11"/>
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
       <c r="AL1" s="51" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AM1" s="11"/>
       <c r="AN1" s="11"/>
@@ -1688,18 +1685,18 @@
       <c r="AU1" s="11"/>
       <c r="AV1" s="11"/>
       <c r="AW1" s="51" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AX1" s="29"/>
       <c r="AY1" s="30"/>
       <c r="AZ1" s="31"/>
       <c r="BA1" s="59" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="BB1" s="61"/>
       <c r="BC1" s="62"/>
       <c r="BD1" s="51" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="BE1" s="61"/>
       <c r="BF1" s="66"/>
@@ -1718,7 +1715,7 @@
       <c r="BS1" s="66"/>
       <c r="BT1" s="62"/>
       <c r="BU1" s="51" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="BV1" s="30"/>
       <c r="BW1" s="30"/>
@@ -1726,13 +1723,13 @@
       <c r="BY1" s="30"/>
       <c r="BZ1" s="12"/>
       <c r="CA1" s="51" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="CB1" s="30"/>
       <c r="CC1" s="30"/>
       <c r="CD1" s="30"/>
       <c r="CE1" s="51" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="CF1" s="30"/>
       <c r="CG1" s="30"/>
@@ -1743,7 +1740,7 @@
       <c r="CL1" s="30"/>
       <c r="CM1" s="30"/>
       <c r="CN1" s="50" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="CO1" s="30"/>
       <c r="CP1" s="30"/>
@@ -1768,11 +1765,11 @@
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="52" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="52"/>
       <c r="E2" s="32" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F2" s="33"/>
       <c r="G2" s="33"/>
@@ -1786,13 +1783,13 @@
       <c r="O2" s="26"/>
       <c r="P2" s="47"/>
       <c r="Q2" s="14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R2" s="15"/>
       <c r="S2" s="16"/>
       <c r="T2" s="33"/>
       <c r="U2" s="53" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="V2" s="54"/>
       <c r="W2" s="54"/>
@@ -1801,7 +1798,7 @@
       <c r="Z2" s="55"/>
       <c r="AA2" s="67"/>
       <c r="AB2" s="56" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AC2" s="57"/>
       <c r="AD2" s="57"/>
@@ -1810,13 +1807,13 @@
       <c r="AG2" s="58"/>
       <c r="AH2" s="67"/>
       <c r="AI2" s="32" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AJ2" s="33"/>
       <c r="AK2" s="34"/>
       <c r="AL2" s="67"/>
       <c r="AM2" s="56" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AN2" s="57"/>
       <c r="AO2" s="57"/>
@@ -1829,18 +1826,18 @@
       <c r="AV2" s="57"/>
       <c r="AW2" s="67"/>
       <c r="AX2" s="56" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AY2" s="57"/>
       <c r="AZ2" s="58"/>
       <c r="BA2" s="60"/>
       <c r="BB2" s="56" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="BC2" s="58"/>
       <c r="BD2" s="67"/>
       <c r="BE2" s="56" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BF2" s="57"/>
       <c r="BG2" s="57"/>
@@ -1859,7 +1856,7 @@
       <c r="BT2" s="58"/>
       <c r="BU2" s="67"/>
       <c r="BV2" s="56" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BW2" s="57"/>
       <c r="BX2" s="57"/>
@@ -1867,7 +1864,7 @@
       <c r="BZ2" s="63"/>
       <c r="CA2" s="67"/>
       <c r="CB2" s="56" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="CC2" s="57"/>
       <c r="CD2" s="58"/>
@@ -1902,310 +1899,310 @@
     </row>
     <row r="3" spans="1:110" s="37" customFormat="1" ht="115.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="C3" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="I3" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="N3" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="O3" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="P3" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="K3" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="L3" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="M3" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="N3" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="O3" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="P3" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q3" s="20" t="s">
+      <c r="S3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="R3" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="S3" s="20" t="s">
-        <v>3</v>
-      </c>
       <c r="T3" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U3" s="64" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="V3" s="65"/>
       <c r="W3" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="X3" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="X3" s="20" t="s">
+      <c r="Y3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="Y3" s="20" t="s">
+      <c r="Z3" s="20" t="s">
         <v>14</v>
-      </c>
-      <c r="Z3" s="20" t="s">
-        <v>15</v>
       </c>
       <c r="AA3" s="67"/>
       <c r="AB3" s="27" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AC3" s="28"/>
       <c r="AD3" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE3" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="AE3" s="20" t="s">
+      <c r="AF3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="AF3" s="20" t="s">
+      <c r="AG3" s="20" t="s">
         <v>14</v>
-      </c>
-      <c r="AG3" s="20" t="s">
-        <v>15</v>
       </c>
       <c r="AH3" s="67"/>
       <c r="AI3" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ3" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="AJ3" s="20" t="s">
+      <c r="AK3" s="20" t="s">
         <v>18</v>
-      </c>
-      <c r="AK3" s="20" t="s">
-        <v>19</v>
       </c>
       <c r="AL3" s="67"/>
       <c r="AM3" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="AN3" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO3" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP3" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="AN3" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="AO3" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="AP3" s="20" t="s">
+      <c r="AQ3" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="AQ3" s="20" t="s">
+      <c r="AR3" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="AR3" s="20" t="s">
+      <c r="AS3" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="AS3" s="20" t="s">
+      <c r="AT3" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU3" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="AT3" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="AU3" s="20" t="s">
-        <v>26</v>
-      </c>
       <c r="AV3" s="20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW3" s="67"/>
       <c r="AX3" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY3" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ3" s="21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BA3" s="60"/>
       <c r="BB3" s="22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC3" s="28" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="BD3" s="67"/>
       <c r="BE3" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="BF3" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="BG3" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="BF3" s="20" t="s">
+      <c r="BH3" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="BG3" s="20" t="s">
+      <c r="BI3" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="BH3" s="20" t="s">
+      <c r="BJ3" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="BI3" s="20" t="s">
+      <c r="BK3" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="BJ3" s="20" t="s">
+      <c r="BL3" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="BK3" s="20" t="s">
+      <c r="BM3" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="BL3" s="20" t="s">
+      <c r="BN3" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="BM3" s="20" t="s">
+      <c r="BO3" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="BN3" s="20" t="s">
+      <c r="BP3" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="BO3" s="20" t="s">
+      <c r="BQ3" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="BP3" s="20" t="s">
+      <c r="BR3" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="BQ3" s="20" t="s">
+      <c r="BS3" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BR3" s="20" t="s">
+      <c r="BT3" s="27" t="s">
         <v>49</v>
-      </c>
-      <c r="BS3" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="BT3" s="27" t="s">
-        <v>51</v>
       </c>
       <c r="BU3" s="67"/>
       <c r="BV3" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="BW3" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="BX3" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="BW3" s="20" t="s">
+      <c r="BY3" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="BZ3" s="20" t="s">
         <v>54</v>
-      </c>
-      <c r="BX3" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="BY3" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="BZ3" s="20" t="s">
-        <v>56</v>
       </c>
       <c r="CA3" s="67"/>
       <c r="CB3" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="CC3" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="CC3" s="21" t="s">
+      <c r="CD3" s="21" t="s">
         <v>30</v>
-      </c>
-      <c r="CD3" s="21" t="s">
-        <v>31</v>
       </c>
       <c r="CE3" s="67"/>
       <c r="CF3" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="CG3" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="CH3" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="CG3" s="23" t="s">
+      <c r="CI3" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="CH3" s="23" t="s">
+      <c r="CJ3" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="CI3" s="23" t="s">
+      <c r="CK3" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="CJ3" s="41" t="s">
+      <c r="CL3" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="CK3" s="23" t="s">
+      <c r="CM3" s="24" t="s">
         <v>99</v>
-      </c>
-      <c r="CL3" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="CM3" s="24" t="s">
-        <v>101</v>
       </c>
       <c r="CN3" s="51"/>
       <c r="CO3" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="CP3" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="CQ3" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="CR3" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="CP3" s="24" t="s">
+      <c r="CS3" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="CT3" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="CU3" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="CQ3" s="24" t="s">
+      <c r="CV3" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="CR3" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="CS3" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="CT3" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="CU3" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="CV3" s="24" t="s">
-        <v>112</v>
-      </c>
       <c r="CW3" s="23" t="s">
-        <v>113</v>
+        <v>229</v>
       </c>
       <c r="CX3" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="CY3" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="CZ3" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="DA3" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="CY3" s="23" t="s">
+      <c r="DB3" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="CZ3" s="23" t="s">
+      <c r="DC3" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="DA3" s="23" t="s">
+      <c r="DD3" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="DE3" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="DB3" s="23" t="s">
+      <c r="DF3" s="23" t="s">
         <v>127</v>
-      </c>
-      <c r="DC3" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="DD3" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="DE3" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="DF3" s="23" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:110" ht="15.75" x14ac:dyDescent="0.25">
@@ -2213,96 +2210,96 @@
         <v>1</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E4" s="46">
         <v>42996</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G4" s="46">
         <v>34497</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Y4" s="1">
         <v>390002</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AA4" s="8"/>
       <c r="AB4" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AD4" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AF4" s="1">
         <v>388150</v>
       </c>
       <c r="AG4" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AH4" s="8"/>
       <c r="AI4" s="1">
@@ -2312,108 +2309,108 @@
         <v>9427240876</v>
       </c>
       <c r="AK4" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AL4" s="8"/>
       <c r="AM4" s="6">
         <v>917010058529274</v>
       </c>
       <c r="AN4" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AO4" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="44"/>
       <c r="AR4" s="44" t="s">
+        <v>146</v>
+      </c>
+      <c r="AS4" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="AT4" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AU4" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="AS4" s="1" t="s">
+      <c r="AV4" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="AT4" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="AU4" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="AV4" s="7" t="s">
-        <v>153</v>
-      </c>
       <c r="AW4" s="8"/>
-      <c r="AX4" s="3" t="s">
-        <v>220</v>
+      <c r="AX4" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="AY4" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AZ4" s="1"/>
       <c r="BA4" s="8"/>
       <c r="BB4" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="BC4" s="45" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="BD4" s="8"/>
       <c r="BE4" s="40" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="BF4" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="BG4" s="40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="BH4" s="46">
         <v>23615</v>
       </c>
       <c r="BI4" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="BJ4" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="BK4" s="46">
         <v>24552</v>
       </c>
       <c r="BL4" s="1"/>
       <c r="BM4" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="BN4" s="46" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="BO4" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="BP4" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="BQ4" s="46" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="BR4" s="1"/>
       <c r="BS4" s="1"/>
       <c r="BT4" s="46" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="BU4" s="8"/>
       <c r="BV4" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="BW4" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="BX4" s="1">
         <v>9979515243</v>
       </c>
       <c r="BY4" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="BZ4" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="CA4" s="8"/>
       <c r="CB4" s="40"/>
@@ -2421,13 +2418,13 @@
       <c r="CD4" s="40"/>
       <c r="CE4" s="8"/>
       <c r="CF4" s="40" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="CG4" s="40" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="CH4" s="40" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="CI4" s="40">
         <v>0</v>
@@ -2436,41 +2433,41 @@
         <v>0</v>
       </c>
       <c r="CK4" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="CL4" s="40" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="CM4" s="40" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="CN4" s="8"/>
       <c r="CO4" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="CP4" s="1">
         <v>8</v>
       </c>
       <c r="CQ4" s="40" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="CR4" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="CS4" s="46">
         <v>43466</v>
       </c>
       <c r="CT4" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="CU4" s="4">
         <v>10000</v>
       </c>
       <c r="CV4" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="CW4" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="CX4" s="1">
         <v>20000</v>
@@ -2479,25 +2476,25 @@
         <v>15000</v>
       </c>
       <c r="CZ4" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="DA4" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="DB4" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="DC4" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="DD4" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="DE4" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="DF4" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:110" ht="15.75" x14ac:dyDescent="0.25">
@@ -2505,96 +2502,96 @@
         <v>2</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E5" s="46">
         <v>43059</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G5" s="46">
         <v>32782</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q5" s="48" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="R5" s="48" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S5" s="48" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Y5" s="3">
         <v>390019</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AA5" s="8"/>
       <c r="AB5" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="AC5" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="AD5" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AF5" s="1">
         <v>391155</v>
       </c>
       <c r="AG5" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AH5" s="8"/>
       <c r="AI5" s="1">
@@ -2604,110 +2601,110 @@
         <v>9712797929</v>
       </c>
       <c r="AK5" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="AL5" s="8"/>
       <c r="AM5" s="6">
         <v>917010058531044</v>
       </c>
       <c r="AN5" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AO5" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="1"/>
       <c r="AR5" s="44" t="s">
+        <v>173</v>
+      </c>
+      <c r="AS5" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="AT5" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="AU5" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="AS5" s="1" t="s">
+      <c r="AV5" s="7" t="s">
         <v>177</v>
-      </c>
-      <c r="AT5" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="AU5" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="AV5" s="7" t="s">
-        <v>180</v>
       </c>
       <c r="AW5" s="8"/>
       <c r="AX5" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AY5" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AZ5" s="1"/>
       <c r="BA5" s="8"/>
       <c r="BB5" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="BC5" s="49" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="BD5" s="8"/>
       <c r="BE5" s="40" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="BF5" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="BG5" s="40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="BH5" s="46">
         <v>22433</v>
       </c>
       <c r="BI5" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="BJ5" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="BK5" s="46">
         <v>25495</v>
       </c>
       <c r="BL5" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="BM5" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="BN5" s="46">
         <v>34533</v>
       </c>
       <c r="BO5" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="BP5" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="BQ5" s="46" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="BR5" s="1"/>
       <c r="BS5" s="1"/>
       <c r="BT5" s="46" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="BU5" s="8"/>
       <c r="BV5" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="BW5" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="BX5" s="1">
         <v>9512287622</v>
       </c>
       <c r="BY5" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="BZ5" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="CA5" s="8"/>
       <c r="CB5" s="40"/>
@@ -2715,56 +2712,56 @@
       <c r="CD5" s="40"/>
       <c r="CE5" s="8"/>
       <c r="CF5" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="CG5" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="CH5" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="CI5" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="CJ5" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="CG5" s="40" t="s">
+      <c r="CK5" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="CH5" s="40" t="s">
-        <v>191</v>
-      </c>
-      <c r="CI5" s="40" t="s">
+      <c r="CL5" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="CM5" s="40" t="s">
         <v>192</v>
-      </c>
-      <c r="CJ5" s="40" t="s">
-        <v>193</v>
-      </c>
-      <c r="CK5" s="40" t="s">
-        <v>194</v>
-      </c>
-      <c r="CL5" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="CM5" s="40" t="s">
-        <v>195</v>
       </c>
       <c r="CN5" s="8"/>
       <c r="CO5" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="CP5" s="1">
         <v>8</v>
       </c>
       <c r="CQ5" s="40" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="CR5" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="CS5" s="46">
         <v>43466</v>
       </c>
       <c r="CT5" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="CU5" s="4">
         <v>10000</v>
       </c>
       <c r="CV5" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="CW5" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="CX5" s="1">
         <v>15000</v>
@@ -2773,25 +2770,25 @@
         <v>15000</v>
       </c>
       <c r="CZ5" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="DA5" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="DB5" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="DC5" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="DD5" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="DE5" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="DF5" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:110" ht="15.75" x14ac:dyDescent="0.25">
@@ -2799,96 +2796,96 @@
         <v>3</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E6" s="46">
         <v>43059</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G6" s="46">
         <v>32660</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="N6" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q6" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="R6" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="R6" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="S6" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="U6" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="T6" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="V6" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Y6" s="1">
         <v>390011</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AA6" s="8"/>
       <c r="AB6" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AC6" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AD6" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AF6" s="1">
         <v>390011</v>
       </c>
       <c r="AG6" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AH6" s="8"/>
       <c r="AI6" s="1">
@@ -2898,108 +2895,108 @@
         <v>9824669768</v>
       </c>
       <c r="AK6" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AL6" s="8"/>
       <c r="AM6" s="6">
         <v>917010058530863</v>
       </c>
       <c r="AN6" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AO6" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="1"/>
       <c r="AR6" s="44" t="s">
+        <v>203</v>
+      </c>
+      <c r="AS6" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="AT6" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="AU6" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="AS6" s="1" t="s">
+      <c r="AV6" s="7" t="s">
         <v>207</v>
-      </c>
-      <c r="AT6" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="AU6" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="AV6" s="7" t="s">
-        <v>210</v>
       </c>
       <c r="AW6" s="8"/>
       <c r="AX6" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AY6" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AZ6" s="1"/>
       <c r="BA6" s="8"/>
       <c r="BB6" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="BC6" s="49" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="BD6" s="8"/>
       <c r="BE6" s="40" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="BF6" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="BG6" s="40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="BH6" s="46">
         <v>22951</v>
       </c>
       <c r="BI6" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="BJ6" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="BK6" s="46">
         <v>24990</v>
       </c>
       <c r="BL6" s="1"/>
       <c r="BM6" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="BN6" s="46" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="BO6" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="BP6" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="BQ6" s="46" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="BR6" s="1"/>
       <c r="BS6" s="1"/>
       <c r="BT6" s="46" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="BU6" s="8"/>
       <c r="BV6" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="BW6" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="BX6" s="1">
         <v>9574119344</v>
       </c>
       <c r="BY6" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="BZ6" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="CA6" s="8"/>
       <c r="CB6" s="40"/>
@@ -3007,13 +3004,13 @@
       <c r="CD6" s="40"/>
       <c r="CE6" s="8"/>
       <c r="CF6" s="40" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="CG6" s="40" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="CH6" s="40" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="CI6" s="40">
         <v>0</v>
@@ -3022,41 +3019,41 @@
         <v>0</v>
       </c>
       <c r="CK6" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="CL6" s="40" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="CM6" s="40" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="CN6" s="8"/>
       <c r="CO6" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="CP6" s="1">
         <v>8</v>
       </c>
       <c r="CQ6" s="40" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="CR6" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="CS6" s="46">
         <v>43466</v>
       </c>
       <c r="CT6" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="CU6" s="4">
         <v>8325</v>
       </c>
       <c r="CV6" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="CW6" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="CX6" s="1">
         <v>15000</v>
@@ -3065,25 +3062,25 @@
         <v>15000</v>
       </c>
       <c r="CZ6" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="DA6" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="DB6" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="DC6" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="DD6" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="DE6" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="DF6" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:110" x14ac:dyDescent="0.25">
